--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Lab Observation: Microbiology, ResourceType Observation</t>
+    <t>This StructureDefinition contains the maps for VistA MICROBIOLOGY (file 63.05) to FHIR Observation</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1295,7 +1295,7 @@
     <t>704319004 |Inherent in|</t>
   </si>
   <si>
-    <t>1616: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (#63.05-.06)</t>
+    <t>++: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (#63.05-.06)</t>
   </si>
   <si>
     <t>Observation.device</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AT$76</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2657" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3251" uniqueCount="556">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-lab</t>
+    <t>http://va.gov/fhir/StructureDefinition/LabObservationObservation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -706,6 +706,188 @@
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category.id</t>
+  </si>
+  <si>
+    <t>Observation.category.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>843: fixed value = laboratory</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Observation.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.category:Laboratory</t>
@@ -797,6 +979,30 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN
+Micro.AntibioticSensitivityComment.LRDFN
+Pathology.Autopsy.LRDFN
+Micro.BacteriologyReports.LRDFN
+Pathology.CytoOrganTissueFunction.StaffIEN
+Micro.MicroAntibioticLevel.LRDFN
+Micro.MicroAudit.LRDFN
+Micro.Microbiology.LRDFN
+Micro.MicroOrderedTest.LRDFN
+Micro.MicroSterilityResults.LRDFN
+Micro.MycobacteriologyReports.LRDFN
+Micro.Mycology.LRDFN
+Micro.MycologyReports.LRDFN
+Micro.Parasitology.LRDFN
+Micro.ParasitologyReports.LRDFN
+Micro.ParasitologyStage.LRDFN
+SStaff.SMicroOrderedTest.LRDFN
+Micro.Virology.LRDFN
+Micro.VirologyReports.LRDFN</t>
+  </si>
+  <si>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -1057,31 +1263,6 @@
     <t>Observation.value[x].coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
     <t>1497: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM &gt; ETIOLOGY FIELD - (#63.05-12 &gt; 63.3-.01 &gt; 61.2-)</t>
   </si>
   <si>
@@ -1089,27 +1270,6 @@
   </si>
   <si>
     <t>Observation.value[x].text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1949,7 +2109,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR65"/>
+  <dimension ref="A1:AT76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.69140625" customWidth="true" bestFit="true"/>
@@ -1994,6 +2154,8 @@
     <col min="42" max="42" width="30.0703125" customWidth="true" bestFit="true"/>
     <col min="43" max="43" width="57.953125" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="217.01953125" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="57.953125" customWidth="true" bestFit="true"/>
+    <col min="46" max="46" width="217.01953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2121,6 +2283,12 @@
       <c r="AR1" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT1" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -2247,6 +2415,12 @@
       <c r="AR2" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS2" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT2" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
@@ -2371,6 +2545,12 @@
       <c r="AR3" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS3" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT3" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
@@ -2497,6 +2677,12 @@
       <c r="AR4" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS4" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT4" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
@@ -2623,6 +2809,12 @@
       <c r="AR5" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS5" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT5" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
@@ -2749,6 +2941,12 @@
       <c r="AR6" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS6" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT6" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
@@ -2875,6 +3073,12 @@
       <c r="AR7" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS7" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT7" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
@@ -3001,6 +3205,12 @@
       <c r="AR8" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT8" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
@@ -3129,6 +3339,12 @@
       <c r="AR9" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS9" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT9" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
@@ -3255,6 +3471,12 @@
       <c r="AR10" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS10" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT10" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
@@ -3379,6 +3601,12 @@
       <c r="AR11" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS11" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT11" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
@@ -3505,6 +3733,12 @@
       <c r="AR12" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS12" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT12" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
@@ -3633,6 +3867,12 @@
       <c r="AR13" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS13" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT13" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
@@ -3761,6 +4001,12 @@
       <c r="AR14" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS14" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT14" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
@@ -3889,6 +4135,12 @@
       <c r="AR15" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS15" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT15" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
@@ -4015,6 +4267,12 @@
       <c r="AR16" t="s" s="2">
         <v>166</v>
       </c>
+      <c r="AS16" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT16" t="s" s="2">
+        <v>166</v>
+      </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
@@ -4139,6 +4397,12 @@
       <c r="AR17" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS17" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT17" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
@@ -4265,6 +4529,12 @@
       <c r="AR18" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS18" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT18" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
@@ -4391,6 +4661,12 @@
       <c r="AR19" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS19" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT19" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
@@ -4517,6 +4793,12 @@
       <c r="AR20" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS20" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT20" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
@@ -4643,6 +4925,12 @@
       <c r="AR21" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT21" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
@@ -4769,29 +5057,33 @@
       <c r="AR22" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS22" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT22" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>40</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>50</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>40</v>
@@ -4800,20 +5092,16 @@
         <v>40</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>212</v>
+        <v>118</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>40</v>
       </c>
@@ -4822,7 +5110,7 @@
         <v>40</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>223</v>
+        <v>40</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>40</v>
@@ -4837,13 +5125,13 @@
         <v>40</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>216</v>
+        <v>40</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>217</v>
+        <v>40</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>40</v>
@@ -4861,19 +5149,19 @@
         <v>40</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>211</v>
+        <v>120</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>40</v>
@@ -4885,10 +5173,10 @@
         <v>40</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>219</v>
+        <v>121</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>220</v>
+        <v>40</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>40</v>
@@ -4897,51 +5185,55 @@
         <v>40</v>
       </c>
       <c r="AR23" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS23" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT23" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>225</v>
+        <v>95</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>226</v>
+        <v>97</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
+        <v>123</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>40</v>
       </c>
@@ -4965,75 +5257,81 @@
         <v>40</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>230</v>
+        <v>40</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>231</v>
+        <v>40</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>224</v>
+        <v>127</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>232</v>
+        <v>40</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>233</v>
+        <v>40</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>234</v>
+        <v>40</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>235</v>
+        <v>121</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>236</v>
+        <v>40</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>237</v>
+        <v>40</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>238</v>
+        <v>40</v>
+      </c>
+      <c r="AS24" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT24" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5041,13 +5339,13 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>40</v>
@@ -5056,19 +5354,19 @@
         <v>51</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>40</v>
@@ -5117,13 +5415,13 @@
         <v>40</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>40</v>
@@ -5132,19 +5430,19 @@
         <v>62</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>245</v>
+        <v>40</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>248</v>
+        <v>40</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>40</v>
@@ -5153,15 +5451,21 @@
         <v>40</v>
       </c>
       <c r="AR25" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS25" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT25" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5172,7 +5476,7 @@
         <v>38</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>40</v>
@@ -5181,20 +5485,18 @@
         <v>40</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>250</v>
+        <v>117</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>251</v>
+        <v>118</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>40</v>
@@ -5243,19 +5545,19 @@
         <v>40</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>249</v>
+        <v>120</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>40</v>
@@ -5264,13 +5566,13 @@
         <v>40</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>234</v>
+        <v>40</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>254</v>
+        <v>121</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>248</v>
+        <v>40</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>40</v>
@@ -5279,26 +5581,32 @@
         <v>40</v>
       </c>
       <c r="AR26" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS26" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT26" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>256</v>
+        <v>95</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>40</v>
@@ -5307,23 +5615,21 @@
         <v>40</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>257</v>
+        <v>96</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>97</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
+        <v>123</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>40</v>
       </c>
@@ -5359,46 +5665,46 @@
         <v>40</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>255</v>
+        <v>127</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>262</v>
+        <v>40</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>263</v>
+        <v>40</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>264</v>
+        <v>121</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>265</v>
+        <v>40</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>40</v>
@@ -5407,19 +5713,25 @@
         <v>40</v>
       </c>
       <c r="AR27" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS27" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT27" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>267</v>
+        <v>40</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5429,7 +5741,7 @@
         <v>50</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>40</v>
@@ -5438,19 +5750,19 @@
         <v>51</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>268</v>
+        <v>64</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>269</v>
+        <v>235</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>271</v>
+        <v>237</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>40</v>
@@ -5487,17 +5799,19 @@
         <v>40</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AC28" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>40</v>
+      </c>
       <c r="AD28" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>38</v>
@@ -5506,25 +5820,25 @@
         <v>50</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>274</v>
+        <v>40</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>275</v>
+        <v>62</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>276</v>
+        <v>40</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>278</v>
+        <v>241</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>279</v>
+        <v>40</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>40</v>
@@ -5533,21 +5847,25 @@
         <v>40</v>
       </c>
       <c r="AR28" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS28" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT28" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>280</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>267</v>
+        <v>40</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5557,7 +5875,7 @@
         <v>50</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>40</v>
@@ -5566,20 +5884,18 @@
         <v>51</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>282</v>
+        <v>117</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>40</v>
       </c>
@@ -5627,7 +5943,7 @@
         <v>40</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>38</v>
@@ -5636,42 +5952,48 @@
         <v>50</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>274</v>
+        <v>40</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>275</v>
+        <v>62</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>276</v>
+        <v>40</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>279</v>
+        <v>40</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>283</v>
+        <v>40</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>284</v>
+        <v>40</v>
+      </c>
+      <c r="AS29" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT29" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5694,18 +6016,18 @@
         <v>51</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>286</v>
+        <v>70</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>287</v>
+        <v>250</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>40</v>
       </c>
@@ -5753,7 +6075,7 @@
         <v>40</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>38</v>
@@ -5774,30 +6096,36 @@
         <v>40</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>292</v>
+        <v>40</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>293</v>
+        <v>40</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>294</v>
+        <v>256</v>
+      </c>
+      <c r="AS30" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT30" t="s" s="2">
+        <v>256</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>295</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>295</v>
+        <v>257</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5808,7 +6136,7 @@
         <v>38</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>40</v>
@@ -5820,17 +6148,17 @@
         <v>51</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>296</v>
+        <v>117</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>297</v>
+        <v>258</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>298</v>
+        <v>259</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>299</v>
+        <v>260</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>40</v>
@@ -5879,13 +6207,13 @@
         <v>40</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>295</v>
+        <v>261</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>40</v>
@@ -5894,19 +6222,19 @@
         <v>62</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>300</v>
+        <v>40</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>301</v>
+        <v>262</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>302</v>
+        <v>263</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>303</v>
+        <v>40</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>40</v>
@@ -5915,15 +6243,21 @@
         <v>40</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>304</v>
+        <v>40</v>
+      </c>
+      <c r="AS31" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT31" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>305</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>305</v>
+        <v>264</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5937,7 +6271,7 @@
         <v>50</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>40</v>
@@ -5946,19 +6280,19 @@
         <v>51</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>306</v>
+        <v>265</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>307</v>
+        <v>266</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>308</v>
+        <v>267</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>310</v>
+        <v>269</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>40</v>
@@ -5995,17 +6329,19 @@
         <v>40</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>40</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>305</v>
+        <v>270</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>38</v>
@@ -6014,46 +6350,50 @@
         <v>50</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>311</v>
+        <v>40</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>312</v>
+        <v>62</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>313</v>
+        <v>40</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>314</v>
+        <v>271</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>315</v>
+        <v>272</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>316</v>
+        <v>40</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR32" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS32" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT32" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>40</v>
       </c>
@@ -6065,7 +6405,7 @@
         <v>50</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>40</v>
@@ -6074,19 +6414,19 @@
         <v>51</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>307</v>
+        <v>274</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>310</v>
+        <v>277</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>40</v>
@@ -6135,7 +6475,7 @@
         <v>40</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>305</v>
+        <v>278</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>38</v>
@@ -6144,56 +6484,64 @@
         <v>50</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>311</v>
+        <v>40</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>312</v>
+        <v>62</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>313</v>
+        <v>40</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>314</v>
+        <v>279</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>315</v>
+        <v>280</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>316</v>
+        <v>40</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR33" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS33" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT33" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>319</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>40</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>50</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>40</v>
@@ -6202,16 +6550,20 @@
         <v>40</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>40</v>
       </c>
@@ -6220,7 +6572,7 @@
         <v>40</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>40</v>
+        <v>283</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>40</v>
@@ -6235,13 +6587,13 @@
         <v>40</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>40</v>
+        <v>216</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>40</v>
+        <v>217</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>40</v>
@@ -6259,19 +6611,19 @@
         <v>40</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>120</v>
+        <v>211</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>40</v>
@@ -6283,10 +6635,10 @@
         <v>40</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>121</v>
+        <v>219</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>40</v>
+        <v>220</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>40</v>
@@ -6295,49 +6647,57 @@
         <v>40</v>
       </c>
       <c r="AR34" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS34" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT34" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>321</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>322</v>
+        <v>284</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>95</v>
+        <v>285</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>97</v>
+        <v>286</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>123</v>
+        <v>287</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>40</v>
       </c>
@@ -6361,75 +6721,81 @@
         <v>40</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>40</v>
+        <v>290</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>40</v>
+        <v>291</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>125</v>
+        <v>40</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>127</v>
+        <v>284</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>40</v>
+        <v>292</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>40</v>
+        <v>293</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>40</v>
+        <v>294</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>121</v>
+        <v>295</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>40</v>
+        <v>296</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>40</v>
+        <v>297</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>40</v>
+        <v>298</v>
+      </c>
+      <c r="AS35" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT35" t="s" s="2">
+        <v>298</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6437,13 +6803,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>40</v>
@@ -6452,19 +6818,19 @@
         <v>51</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>329</v>
+        <v>304</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>40</v>
@@ -6513,13 +6879,13 @@
         <v>40</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>40</v>
@@ -6528,36 +6894,42 @@
         <v>62</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>40</v>
+        <v>305</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>40</v>
+        <v>309</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>333</v>
+        <v>310</v>
+      </c>
+      <c r="AS36" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AT36" t="s" s="2">
+        <v>310</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6568,7 +6940,7 @@
         <v>38</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>40</v>
@@ -6580,20 +6952,18 @@
         <v>51</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>117</v>
+        <v>312</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>40</v>
       </c>
@@ -6641,13 +7011,13 @@
         <v>40</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>40</v>
@@ -6662,13 +7032,13 @@
         <v>40</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>40</v>
@@ -6677,19 +7047,25 @@
         <v>40</v>
       </c>
       <c r="AR37" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS37" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT37" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>40</v>
+        <v>318</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6699,28 +7075,28 @@
         <v>50</v>
       </c>
       <c r="H38" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J38" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="I38" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>40</v>
-      </c>
       <c r="K38" t="s" s="2">
-        <v>139</v>
+        <v>319</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>345</v>
+        <v>321</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>346</v>
+        <v>322</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>347</v>
+        <v>323</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>40</v>
@@ -6745,11 +7121,13 @@
         <v>40</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>40</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>348</v>
+        <v>40</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>40</v>
@@ -6767,7 +7145,7 @@
         <v>40</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>38</v>
@@ -6776,25 +7154,25 @@
         <v>50</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>349</v>
+        <v>40</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>62</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>40</v>
+        <v>324</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>93</v>
+        <v>325</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>350</v>
+        <v>326</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>40</v>
+        <v>327</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>40</v>
@@ -6803,50 +7181,56 @@
         <v>40</v>
       </c>
       <c r="AR38" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS38" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT38" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>139</v>
+        <v>330</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>40</v>
@@ -6871,110 +7255,116 @@
         <v>40</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>357</v>
+        <v>40</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>358</v>
+        <v>40</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="AC39" s="2"/>
       <c r="AD39" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>40</v>
+        <v>336</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>62</v>
+        <v>337</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>40</v>
+        <v>338</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>359</v>
+        <v>40</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>40</v>
+        <v>341</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>362</v>
+        <v>40</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR39" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS39" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT39" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="D40" t="s" s="2">
-        <v>40</v>
+        <v>329</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>365</v>
+        <v>331</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>366</v>
+        <v>332</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>367</v>
+        <v>333</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>368</v>
+        <v>334</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>40</v>
@@ -7023,51 +7413,57 @@
         <v>40</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>363</v>
+        <v>328</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>40</v>
+        <v>336</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>62</v>
+        <v>337</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>40</v>
+        <v>338</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>369</v>
+        <v>339</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>40</v>
+        <v>341</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>371</v>
+        <v>345</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>372</v>
+        <v>346</v>
+      </c>
+      <c r="AS40" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AT40" t="s" s="2">
+        <v>346</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>347</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>373</v>
+        <v>347</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7087,19 +7483,19 @@
         <v>40</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>139</v>
+        <v>348</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7125,13 +7521,13 @@
         <v>40</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>377</v>
+        <v>40</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>378</v>
+        <v>40</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>379</v>
+        <v>40</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>40</v>
@@ -7149,7 +7545,7 @@
         <v>40</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>373</v>
+        <v>347</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>38</v>
@@ -7167,33 +7563,39 @@
         <v>40</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>380</v>
+        <v>40</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>40</v>
+        <v>354</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>383</v>
+        <v>40</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>40</v>
+        <v>355</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>40</v>
+        <v>356</v>
+      </c>
+      <c r="AS41" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AT41" t="s" s="2">
+        <v>356</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>384</v>
+        <v>357</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>384</v>
+        <v>357</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7204,7 +7606,7 @@
         <v>38</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>40</v>
@@ -7213,22 +7615,20 @@
         <v>40</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>139</v>
+        <v>358</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>388</v>
+        <v>361</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>40</v>
@@ -7253,13 +7653,13 @@
         <v>40</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>377</v>
+        <v>40</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>389</v>
+        <v>40</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>390</v>
+        <v>40</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>40</v>
@@ -7277,13 +7677,13 @@
         <v>40</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>384</v>
+        <v>357</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>40</v>
@@ -7292,19 +7692,19 @@
         <v>62</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>40</v>
+        <v>362</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>40</v>
+        <v>365</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>40</v>
@@ -7313,15 +7713,21 @@
         <v>40</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>40</v>
+        <v>366</v>
+      </c>
+      <c r="AS42" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT42" t="s" s="2">
+        <v>366</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7335,27 +7741,29 @@
         <v>50</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>40</v>
       </c>
@@ -7391,19 +7799,17 @@
         <v>40</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>38</v>
@@ -7412,44 +7818,52 @@
         <v>50</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>40</v>
+        <v>373</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>62</v>
+        <v>374</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>398</v>
+        <v>375</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>399</v>
+        <v>376</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>400</v>
+        <v>377</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>401</v>
+        <v>378</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>402</v>
+        <v>40</v>
+      </c>
+      <c r="AS43" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT43" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>40</v>
       </c>
@@ -7461,27 +7875,29 @@
         <v>50</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>404</v>
+        <v>139</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>405</v>
+        <v>369</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>406</v>
+        <v>370</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>40</v>
       </c>
@@ -7529,7 +7945,7 @@
         <v>40</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>403</v>
+        <v>367</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>38</v>
@@ -7538,42 +7954,48 @@
         <v>50</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>40</v>
+        <v>373</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>62</v>
+        <v>374</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>408</v>
+        <v>375</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR44" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS44" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT44" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7584,7 +8006,7 @@
         <v>38</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>40</v>
@@ -7596,20 +8018,16 @@
         <v>40</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>413</v>
+        <v>117</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>414</v>
+        <v>118</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>40</v>
       </c>
@@ -7657,19 +8075,19 @@
         <v>40</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>412</v>
+        <v>120</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>418</v>
+        <v>40</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>40</v>
@@ -7678,10 +8096,10 @@
         <v>40</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>419</v>
+        <v>40</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>420</v>
+        <v>121</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>40</v>
@@ -7693,26 +8111,32 @@
         <v>40</v>
       </c>
       <c r="AR45" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS45" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT45" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>421</v>
+        <v>383</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>421</v>
+        <v>384</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>40</v>
@@ -7724,15 +8148,17 @@
         <v>40</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>99</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>40</v>
@@ -7769,31 +8195,31 @@
         <v>40</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>40</v>
@@ -7817,19 +8243,25 @@
         <v>40</v>
       </c>
       <c r="AR46" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS46" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT46" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>422</v>
+        <v>385</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>422</v>
+        <v>386</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7845,21 +8277,23 @@
         <v>40</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>96</v>
+        <v>224</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>123</v>
+        <v>226</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>40</v>
       </c>
@@ -7907,7 +8341,7 @@
         <v>40</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>127</v>
+        <v>229</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>38</v>
@@ -7919,7 +8353,7 @@
         <v>40</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>40</v>
@@ -7928,10 +8362,10 @@
         <v>40</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>121</v>
+        <v>231</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>40</v>
@@ -7943,50 +8377,56 @@
         <v>40</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>40</v>
+        <v>387</v>
+      </c>
+      <c r="AS47" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT47" t="s" s="2">
+        <v>387</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>423</v>
+        <v>388</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>423</v>
+        <v>389</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>424</v>
+        <v>40</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>40</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>51</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>425</v>
+        <v>274</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>426</v>
+        <v>275</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>99</v>
+        <v>276</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>105</v>
+        <v>277</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>40</v>
@@ -8035,19 +8475,19 @@
         <v>40</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>427</v>
+        <v>278</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>40</v>
@@ -8056,10 +8496,10 @@
         <v>40</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>40</v>
+        <v>279</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>93</v>
+        <v>280</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>40</v>
@@ -8071,15 +8511,21 @@
         <v>40</v>
       </c>
       <c r="AR48" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS48" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT48" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>428</v>
+        <v>390</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>428</v>
+        <v>390</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8093,7 +8539,7 @@
         <v>50</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>40</v>
@@ -8102,16 +8548,20 @@
         <v>40</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>429</v>
+        <v>139</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>430</v>
+        <v>391</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>40</v>
       </c>
@@ -8135,13 +8585,11 @@
         <v>40</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>40</v>
+        <v>395</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>40</v>
@@ -8159,7 +8607,7 @@
         <v>40</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>428</v>
+        <v>390</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>38</v>
@@ -8168,7 +8616,7 @@
         <v>50</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>432</v>
+        <v>396</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>62</v>
@@ -8180,10 +8628,10 @@
         <v>40</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>433</v>
+        <v>93</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>434</v>
+        <v>397</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>40</v>
@@ -8195,26 +8643,32 @@
         <v>40</v>
       </c>
       <c r="AR49" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS49" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT49" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>435</v>
+        <v>398</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>435</v>
+        <v>398</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>40</v>
+        <v>399</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>40</v>
@@ -8226,16 +8680,20 @@
         <v>40</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>429</v>
+        <v>139</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>436</v>
+        <v>400</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>40</v>
       </c>
@@ -8259,13 +8717,13 @@
         <v>40</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>40</v>
+        <v>404</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>40</v>
+        <v>405</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>40</v>
@@ -8283,16 +8741,16 @@
         <v>40</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>435</v>
+        <v>398</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>432</v>
+        <v>40</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>62</v>
@@ -8301,33 +8759,39 @@
         <v>40</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>40</v>
+        <v>406</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>433</v>
+        <v>407</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>438</v>
+        <v>408</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>40</v>
+        <v>409</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR50" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS50" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT50" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>439</v>
+        <v>410</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>439</v>
+        <v>410</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8338,7 +8802,7 @@
         <v>38</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>40</v>
@@ -8350,19 +8814,19 @@
         <v>40</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>139</v>
+        <v>411</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>440</v>
+        <v>412</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>441</v>
+        <v>413</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>442</v>
+        <v>414</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>443</v>
+        <v>415</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>40</v>
@@ -8387,13 +8851,13 @@
         <v>40</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>444</v>
+        <v>40</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>445</v>
+        <v>40</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>40</v>
@@ -8411,13 +8875,13 @@
         <v>40</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>439</v>
+        <v>410</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>40</v>
@@ -8429,13 +8893,13 @@
         <v>40</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>446</v>
+        <v>40</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>361</v>
+        <v>417</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>40</v>
@@ -8444,18 +8908,24 @@
         <v>40</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>40</v>
+        <v>418</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>40</v>
+        <v>419</v>
+      </c>
+      <c r="AS51" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AT51" t="s" s="2">
+        <v>419</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8466,7 +8936,7 @@
         <v>38</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>40</v>
@@ -8481,17 +8951,15 @@
         <v>139</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>449</v>
+        <v>421</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>40</v>
       </c>
@@ -8515,13 +8983,13 @@
         <v>40</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>377</v>
+        <v>424</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>454</v>
+        <v>426</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>40</v>
@@ -8539,13 +9007,13 @@
         <v>40</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>40</v>
@@ -8557,33 +9025,39 @@
         <v>40</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>361</v>
+        <v>429</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>40</v>
+        <v>430</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR52" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS52" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT52" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8606,17 +9080,19 @@
         <v>40</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>456</v>
+        <v>139</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>40</v>
@@ -8641,13 +9117,13 @@
         <v>40</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>40</v>
+        <v>424</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>40</v>
+        <v>436</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>40</v>
+        <v>437</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>40</v>
@@ -8665,7 +9141,7 @@
         <v>40</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>38</v>
@@ -8686,10 +9162,10 @@
         <v>40</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>40</v>
+        <v>438</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>40</v>
@@ -8701,15 +9177,21 @@
         <v>40</v>
       </c>
       <c r="AR53" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS53" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT53" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>461</v>
+        <v>440</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>461</v>
+        <v>440</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8732,15 +9214,17 @@
         <v>40</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>117</v>
+        <v>441</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>462</v>
+        <v>442</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>40</v>
@@ -8789,7 +9273,7 @@
         <v>40</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>461</v>
+        <v>440</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>38</v>
@@ -8807,33 +9291,39 @@
         <v>40</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>40</v>
+        <v>445</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>40</v>
+        <v>448</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>40</v>
+        <v>449</v>
+      </c>
+      <c r="AS54" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT54" t="s" s="2">
+        <v>449</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8844,7 +9334,7 @@
         <v>38</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>40</v>
@@ -8853,19 +9343,19 @@
         <v>40</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8915,13 +9405,13 @@
         <v>40</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>40</v>
@@ -8933,33 +9423,39 @@
         <v>40</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>40</v>
+        <v>455</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>40</v>
+        <v>458</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR55" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS55" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT55" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8979,21 +9475,23 @@
         <v>40</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>40</v>
       </c>
@@ -9041,7 +9539,7 @@
         <v>40</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>38</v>
@@ -9053,7 +9551,7 @@
         <v>40</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>62</v>
+        <v>465</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>40</v>
@@ -9062,10 +9560,10 @@
         <v>40</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>40</v>
@@ -9077,15 +9575,21 @@
         <v>40</v>
       </c>
       <c r="AR56" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS56" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT56" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9096,7 +9600,7 @@
         <v>38</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>40</v>
@@ -9105,23 +9609,19 @@
         <v>40</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>413</v>
+        <v>117</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>479</v>
+        <v>118</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>40</v>
       </c>
@@ -9169,19 +9669,19 @@
         <v>40</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>478</v>
+        <v>120</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>40</v>
@@ -9190,10 +9690,10 @@
         <v>40</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>483</v>
+        <v>40</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>484</v>
+        <v>121</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>40</v>
@@ -9205,26 +9705,32 @@
         <v>40</v>
       </c>
       <c r="AR57" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS57" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT57" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>40</v>
@@ -9236,15 +9742,17 @@
         <v>40</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>99</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>40</v>
@@ -9293,19 +9801,19 @@
         <v>40</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>40</v>
@@ -9329,19 +9837,25 @@
         <v>40</v>
       </c>
       <c r="AR58" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS58" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT58" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>95</v>
+        <v>471</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9354,24 +9868,26 @@
         <v>40</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>96</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>97</v>
+        <v>472</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>123</v>
+        <v>473</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>40</v>
       </c>
@@ -9419,7 +9935,7 @@
         <v>40</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>127</v>
+        <v>474</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>38</v>
@@ -9443,7 +9959,7 @@
         <v>40</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>40</v>
@@ -9455,51 +9971,53 @@
         <v>40</v>
       </c>
       <c r="AR59" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS59" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT59" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>424</v>
+        <v>40</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>40</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>96</v>
+        <v>476</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>425</v>
+        <v>477</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>40</v>
       </c>
@@ -9547,19 +10065,19 @@
         <v>40</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>427</v>
+        <v>475</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>40</v>
+        <v>479</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>40</v>
@@ -9568,10 +10086,10 @@
         <v>40</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>40</v>
+        <v>480</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>93</v>
+        <v>481</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>40</v>
@@ -9583,15 +10101,21 @@
         <v>40</v>
       </c>
       <c r="AR60" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS60" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT60" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9599,7 +10123,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>50</v>
@@ -9611,23 +10135,19 @@
         <v>40</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>139</v>
+        <v>476</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>40</v>
       </c>
@@ -9651,13 +10171,13 @@
         <v>40</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>377</v>
+        <v>40</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>492</v>
+        <v>40</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>231</v>
+        <v>40</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>40</v>
@@ -9675,16 +10195,16 @@
         <v>40</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>50</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>40</v>
+        <v>479</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>62</v>
@@ -9693,16 +10213,16 @@
         <v>40</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>493</v>
+        <v>40</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>234</v>
+        <v>480</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>235</v>
+        <v>485</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>236</v>
+        <v>40</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>40</v>
@@ -9711,15 +10231,21 @@
         <v>40</v>
       </c>
       <c r="AR61" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS61" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT61" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9739,22 +10265,22 @@
         <v>40</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>306</v>
+        <v>139</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>310</v>
+        <v>490</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>40</v>
@@ -9779,13 +10305,13 @@
         <v>40</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>40</v>
+        <v>491</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>40</v>
+        <v>492</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>40</v>
@@ -9803,7 +10329,7 @@
         <v>40</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>38</v>
@@ -9821,33 +10347,39 @@
         <v>40</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>314</v>
+        <v>494</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>315</v>
+        <v>408</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>316</v>
+        <v>40</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT62" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9858,7 +10390,7 @@
         <v>38</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>40</v>
@@ -9873,16 +10405,16 @@
         <v>139</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>347</v>
+        <v>499</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>40</v>
@@ -9907,13 +10439,13 @@
         <v>40</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>144</v>
+        <v>424</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>348</v>
+        <v>501</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>40</v>
@@ -9931,16 +10463,16 @@
         <v>40</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>504</v>
+        <v>40</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>62</v>
@@ -9949,13 +10481,13 @@
         <v>40</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>40</v>
+        <v>493</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>93</v>
+        <v>494</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>350</v>
+        <v>408</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>40</v>
@@ -9967,26 +10499,32 @@
         <v>40</v>
       </c>
       <c r="AR63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT63" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>352</v>
+        <v>40</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>40</v>
@@ -9998,19 +10536,17 @@
         <v>40</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>139</v>
+        <v>503</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>353</v>
+        <v>504</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>356</v>
+        <v>506</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>40</v>
@@ -10035,13 +10571,13 @@
         <v>40</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>357</v>
+        <v>40</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>358</v>
+        <v>40</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>40</v>
@@ -10059,13 +10595,13 @@
         <v>40</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>40</v>
@@ -10077,33 +10613,39 @@
         <v>40</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>359</v>
+        <v>40</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>360</v>
+        <v>40</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>361</v>
+        <v>507</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>362</v>
+        <v>40</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT64" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10114,7 +10656,7 @@
         <v>38</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>40</v>
@@ -10126,20 +10668,16 @@
         <v>40</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>40</v>
       </c>
@@ -10187,13 +10725,13 @@
         <v>40</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>40</v>
@@ -10208,10 +10746,10 @@
         <v>40</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>419</v>
+        <v>480</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>420</v>
+        <v>511</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>40</v>
@@ -10223,11 +10761,1481 @@
         <v>40</v>
       </c>
       <c r="AR65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT65" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT66" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT67" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT68" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT69" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT70" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT71" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT72" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT73" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT74" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT75" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT76" t="s" s="2">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR65">
+  <autoFilter ref="A1:AT76">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10237,7 +12245,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI64">
+  <conditionalFormatting sqref="A2:AI75">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3297" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3297" uniqueCount="600">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -255,10 +255,10 @@
     <t>Mapping: SNOMED CT Attribute Binding</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -938,6 +938,10 @@
   </si>
   <si>
     <t>Coding.code</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-8:843: fixed value "laboratory" {null}</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1111,6 +1115,9 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN
@@ -1134,9 +1141,6 @@
 Micro.VirologyReports.LRDFN</t>
   </si>
   <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
-  </si>
-  <si>
     <t>Observation.focus</t>
   </si>
   <si>
@@ -1246,6 +1250,9 @@
   <si>
     <t xml:space="preserve">dateTime
 </t>
+  </si>
+  <si>
+    <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (#63.05-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime
@@ -1267,9 +1274,6 @@
 Micro.VirologyReports.SpecimenTakenDateTime</t>
   </si>
   <si>
-    <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (#63.05-.01)</t>
-  </si>
-  <si>
     <t>Observation.issued</t>
   </si>
   <si>
@@ -1295,10 +1299,10 @@
     <t>FiveWs.recorded</t>
   </si>
   <si>
+    <t>1484: source value from MICROBIOLOGY - DATE REPORT COMPLETED (#63.05-.03)</t>
+  </si>
+  <si>
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
-  </si>
-  <si>
-    <t>1484: source value from MICROBIOLOGY - DATE REPORT COMPLETED (#63.05-.03)</t>
   </si>
   <si>
     <t>Observation.performer</t>
@@ -1488,10 +1492,10 @@
     <t>subjectOf.observationEvent[code="annotation"].value</t>
   </si>
   <si>
+    <t>1455: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - COMMENT &gt; COMMENT - COMMENT (#63.05-12 &gt; 63.3-2 &gt; 63.31-.01)</t>
+  </si>
+  <si>
     <t>Micro.Microbiology.SpecimenComment</t>
-  </si>
-  <si>
-    <t>1455: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - COMMENT &gt; COMMENT - COMMENT (#63.05-12 &gt; 63.3-2 &gt; 63.31-.01)</t>
   </si>
   <si>
     <t>Observation.bodySite</t>
@@ -2281,10 +2285,10 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="57.953125" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="217.01953125" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="57.953125" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="217.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="217.01953125" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="57.953125" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="217.01953125" customWidth="true" bestFit="true"/>
+    <col min="46" max="46" width="57.953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4531,16 +4535,16 @@
         <v>84</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="AR17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AS17" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AT17" t="s" s="2">
-        <v>210</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -6356,7 +6360,7 @@
         <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>298</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>84</v>
@@ -6365,10 +6369,10 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>84</v>
@@ -6377,24 +6381,24 @@
         <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>84</v>
+        <v>301</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>300</v>
+        <v>84</v>
       </c>
       <c r="AS31" t="s" s="2">
-        <v>84</v>
+        <v>301</v>
       </c>
       <c r="AT31" t="s" s="2">
-        <v>300</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6420,14 +6424,14 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6476,7 +6480,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6497,10 +6501,10 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>84</v>
@@ -6523,10 +6527,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6549,19 +6553,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6610,7 +6614,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6631,10 +6635,10 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
@@ -6657,10 +6661,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6686,16 +6690,16 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6744,7 +6748,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6765,10 +6769,10 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
@@ -6791,13 +6795,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>255</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>84</v>
@@ -6841,7 +6845,7 @@
         <v>84</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>84</v>
@@ -6927,14 +6931,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6956,16 +6960,16 @@
         <v>183</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6993,10 +6997,10 @@
         <v>188</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -7014,7 +7018,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>94</v>
@@ -7029,42 +7033,42 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>342</v>
+        <v>84</v>
       </c>
       <c r="AS36" t="s" s="2">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="AT36" t="s" s="2">
-        <v>342</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7087,19 +7091,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -7148,7 +7152,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7163,42 +7167,42 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AR37" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AS37" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AS37" t="s" s="2">
-        <v>353</v>
-      </c>
       <c r="AT37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7221,16 +7225,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7280,7 +7284,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7301,13 +7305,13 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>84</v>
@@ -7327,14 +7331,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7353,19 +7357,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7414,7 +7418,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7429,19 +7433,19 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>84</v>
@@ -7461,14 +7465,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7487,19 +7491,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7536,7 +7540,7 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7546,7 +7550,7 @@
         <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7555,25 +7559,25 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>84</v>
@@ -7593,16 +7597,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7621,19 +7625,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7682,7 +7686,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7691,48 +7695,48 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AR41" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AS41" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AS41" t="s" s="2">
-        <v>389</v>
-      </c>
       <c r="AT41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7755,16 +7759,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7814,7 +7818,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7835,36 +7839,36 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AR42" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AS42" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AS42" t="s" s="2">
-        <v>399</v>
-      </c>
       <c r="AT42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7890,14 +7894,14 @@
         <v>219</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7946,7 +7950,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7961,42 +7965,42 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>84</v>
+        <v>410</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>409</v>
+        <v>84</v>
       </c>
       <c r="AS43" t="s" s="2">
-        <v>84</v>
+        <v>410</v>
       </c>
       <c r="AT43" t="s" s="2">
-        <v>409</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8019,19 +8023,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -8068,7 +8072,7 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
@@ -8078,7 +8082,7 @@
         <v>170</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8087,28 +8091,28 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -8125,13 +8129,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>84</v>
@@ -8156,16 +8160,16 @@
         <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8214,7 +8218,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8223,28 +8227,28 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -8261,10 +8265,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8391,10 +8395,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8523,10 +8527,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8643,24 +8647,24 @@
         <v>84</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>84</v>
+        <v>431</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>430</v>
+        <v>84</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>84</v>
+        <v>431</v>
       </c>
       <c r="AT48" t="s" s="2">
-        <v>430</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8686,16 +8690,16 @@
         <v>161</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8744,7 +8748,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8765,10 +8769,10 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
@@ -8791,10 +8795,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8820,16 +8824,16 @@
         <v>183</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8858,7 +8862,7 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8876,7 +8880,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8885,7 +8889,7 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -8900,7 +8904,7 @@
         <v>137</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -8923,14 +8927,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8952,16 +8956,16 @@
         <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8989,10 +8993,10 @@
         <v>188</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -9010,7 +9014,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9028,19 +9032,19 @@
         <v>84</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -9057,10 +9061,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9083,19 +9087,19 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -9144,7 +9148,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9165,10 +9169,10 @@
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -9177,24 +9181,24 @@
         <v>84</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AR52" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AS52" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AS52" t="s" s="2">
-        <v>461</v>
-      </c>
       <c r="AT52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9220,13 +9224,13 @@
         <v>183</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9252,13 +9256,13 @@
         <v>84</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
@@ -9276,7 +9280,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9294,19 +9298,19 @@
         <v>84</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9323,10 +9327,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9352,16 +9356,16 @@
         <v>183</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9386,13 +9390,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9410,7 +9414,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9431,10 +9435,10 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
@@ -9457,10 +9461,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9483,16 +9487,16 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9542,7 +9546,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9560,39 +9564,39 @@
         <v>84</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>84</v>
+        <v>493</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>492</v>
+        <v>84</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>84</v>
+        <v>493</v>
       </c>
       <c r="AT55" t="s" s="2">
-        <v>492</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9615,16 +9619,16 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9674,7 +9678,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9692,19 +9696,19 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9721,10 +9725,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9747,19 +9751,19 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9808,7 +9812,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9820,7 +9824,7 @@
         <v>84</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>84</v>
@@ -9829,10 +9833,10 @@
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
@@ -9855,10 +9859,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9985,10 +9989,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10117,14 +10121,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -10146,10 +10150,10 @@
         <v>140</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>143</v>
@@ -10204,7 +10208,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10251,10 +10255,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10277,13 +10281,13 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10334,7 +10338,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10343,7 +10347,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -10355,10 +10359,10 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -10381,10 +10385,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10407,13 +10411,13 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10464,7 +10468,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10473,7 +10477,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -10485,10 +10489,10 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
@@ -10511,10 +10515,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10540,16 +10544,16 @@
         <v>183</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10577,10 +10581,10 @@
         <v>118</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>84</v>
@@ -10598,7 +10602,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10616,13 +10620,13 @@
         <v>84</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
@@ -10645,10 +10649,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10674,16 +10678,16 @@
         <v>183</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10708,13 +10712,13 @@
         <v>84</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10732,7 +10736,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10750,13 +10754,13 @@
         <v>84</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10779,10 +10783,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10805,17 +10809,17 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10864,7 +10868,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10888,7 +10892,7 @@
         <v>84</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
@@ -10911,10 +10915,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10940,10 +10944,10 @@
         <v>161</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10994,7 +10998,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11015,10 +11019,10 @@
         <v>84</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
@@ -11041,10 +11045,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11067,16 +11071,16 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -11126,7 +11130,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11147,10 +11151,10 @@
         <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
@@ -11173,10 +11177,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11199,16 +11203,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11258,7 +11262,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11279,10 +11283,10 @@
         <v>84</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
@@ -11305,10 +11309,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11331,19 +11335,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -11392,7 +11396,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11413,10 +11417,10 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>
@@ -11439,10 +11443,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11569,10 +11573,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11701,14 +11705,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11730,10 +11734,10 @@
         <v>140</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>143</v>
@@ -11788,7 +11792,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11835,10 +11839,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11864,16 +11868,16 @@
         <v>183</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
@@ -11898,13 +11902,13 @@
         <v>84</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>84</v>
@@ -11922,7 +11926,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>94</v>
@@ -11940,16 +11944,16 @@
         <v>84</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>84</v>
@@ -11969,10 +11973,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11995,19 +11999,19 @@
         <v>95</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -12056,7 +12060,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12074,19 +12078,19 @@
         <v>84</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12103,10 +12107,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12132,16 +12136,16 @@
         <v>183</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -12169,10 +12173,10 @@
         <v>188</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>84</v>
@@ -12190,7 +12194,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12199,7 +12203,7 @@
         <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>106</v>
@@ -12214,7 +12218,7 @@
         <v>137</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>84</v>
@@ -12237,14 +12241,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -12266,16 +12270,16 @@
         <v>183</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -12303,10 +12307,10 @@
         <v>188</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -12324,7 +12328,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12342,19 +12346,19 @@
         <v>84</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -12371,10 +12375,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12400,16 +12404,16 @@
         <v>85</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12458,7 +12462,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12479,10 +12483,10 @@
         <v>84</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -941,7 +941,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-8:843: fixed value "laboratory" {null}</t>
+inv-9:843: fixed value = laboratory {null}</t>
   </si>
   <si>
     <t>C*E.1</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3297" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3297" uniqueCount="601">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -941,7 +941,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-9:843: fixed value = laboratory {null}</t>
+inv-10:843: fixed value = laboratory {null}</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1587,7 +1587,10 @@
     <t>704319004 |Inherent in|</t>
   </si>
   <si>
-    <t>++: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (#63.05-.06)</t>
+    <t>1659: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (#63.05-.06)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.MicrobiologyAccession</t>
   </si>
   <si>
     <t>Observation.device</t>
@@ -9582,21 +9585,21 @@
         <v>493</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>84</v>
+        <v>494</v>
       </c>
       <c r="AS55" t="s" s="2">
         <v>493</v>
       </c>
       <c r="AT55" t="s" s="2">
-        <v>84</v>
+        <v>494</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9619,16 +9622,16 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9678,7 +9681,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9696,19 +9699,19 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9725,10 +9728,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9751,19 +9754,19 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9812,7 +9815,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9824,7 +9827,7 @@
         <v>84</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>84</v>
@@ -9833,10 +9836,10 @@
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
@@ -9859,10 +9862,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9989,10 +9992,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10121,14 +10124,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -10150,10 +10153,10 @@
         <v>140</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>143</v>
@@ -10208,7 +10211,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10255,10 +10258,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10281,13 +10284,13 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10338,7 +10341,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10347,7 +10350,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -10359,10 +10362,10 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -10385,10 +10388,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10411,13 +10414,13 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10468,7 +10471,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10477,7 +10480,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -10489,10 +10492,10 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
@@ -10515,10 +10518,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10544,16 +10547,16 @@
         <v>183</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10581,10 +10584,10 @@
         <v>118</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>84</v>
@@ -10602,7 +10605,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10620,10 +10623,10 @@
         <v>84</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>452</v>
@@ -10649,10 +10652,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10678,16 +10681,16 @@
         <v>183</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10715,10 +10718,10 @@
         <v>468</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10736,7 +10739,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10754,10 +10757,10 @@
         <v>84</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>452</v>
@@ -10783,10 +10786,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10809,17 +10812,17 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10868,7 +10871,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10892,7 +10895,7 @@
         <v>84</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
@@ -10915,10 +10918,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10944,10 +10947,10 @@
         <v>161</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10998,7 +11001,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11019,10 +11022,10 @@
         <v>84</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
@@ -11045,10 +11048,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11071,16 +11074,16 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -11130,7 +11133,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11151,10 +11154,10 @@
         <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
@@ -11177,10 +11180,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11203,16 +11206,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11262,7 +11265,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11283,10 +11286,10 @@
         <v>84</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
@@ -11309,10 +11312,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11335,19 +11338,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -11396,7 +11399,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11417,10 +11420,10 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>
@@ -11443,10 +11446,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11573,10 +11576,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11705,14 +11708,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11734,10 +11737,10 @@
         <v>140</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>143</v>
@@ -11792,7 +11795,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11839,10 +11842,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11868,13 +11871,13 @@
         <v>183</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>334</v>
@@ -11905,7 +11908,7 @@
         <v>468</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z73" t="s" s="2">
         <v>336</v>
@@ -11926,7 +11929,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>94</v>
@@ -11944,7 +11947,7 @@
         <v>84</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>339</v>
@@ -11973,10 +11976,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12002,13 +12005,13 @@
         <v>412</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>416</v>
@@ -12060,7 +12063,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12078,7 +12081,7 @@
         <v>84</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>420</v>
@@ -12107,10 +12110,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12136,13 +12139,13 @@
         <v>183</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O75" t="s" s="2">
         <v>438</v>
@@ -12173,7 +12176,7 @@
         <v>188</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="Z75" t="s" s="2">
         <v>439</v>
@@ -12194,7 +12197,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12203,7 +12206,7 @@
         <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>106</v>
@@ -12241,10 +12244,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12328,7 +12331,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12375,10 +12378,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12404,16 +12407,16 @@
         <v>85</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12462,7 +12465,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12483,10 +12486,10 @@
         <v>84</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA MICROBIOLOGY (file 63.05) to FHIR Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (#63.05) to LabObservationObservation</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AT$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3297" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2701" uniqueCount="553">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Lab Observation: Microbiology {Observation}</t>
+    <t>Lab Observation: Microbiology Observation</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (#63.05) to LabObservationObservation</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (#63.05) to us-core-observation-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/StructureDefinition/LabObservationObservation</t>
+    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-lab</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -838,192 +838,6 @@
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category.id</t>
-  </si>
-  <si>
-    <t>Observation.category.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-10:843: fixed value = laboratory {null}</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>843: fixed value = laboratory</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Observation.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.category:Laboratory</t>
@@ -1115,30 +929,6 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
-  </si>
-  <si>
-    <t>Micro.AntibioticSensitivity.LRDFN
-Micro.AntibioticSensitivityComment.LRDFN
-Pathology.Autopsy.LRDFN
-Micro.BacteriologyReports.LRDFN
-Pathology.CytoOrganTissueFunction.StaffIEN
-Micro.MicroAntibioticLevel.LRDFN
-Micro.MicroAudit.LRDFN
-Micro.Microbiology.LRDFN
-Micro.MicroOrderedTest.LRDFN
-Micro.MicroSterilityResults.LRDFN
-Micro.MycobacteriologyReports.LRDFN
-Micro.Mycology.LRDFN
-Micro.MycologyReports.LRDFN
-Micro.Parasitology.LRDFN
-Micro.ParasitologyReports.LRDFN
-Micro.ParasitologyStage.LRDFN
-SStaff.SMicroOrderedTest.LRDFN
-Micro.Virology.LRDFN
-Micro.VirologyReports.LRDFN</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -1395,6 +1185,31 @@
     <t>Observation.value[x].coding</t>
   </si>
   <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
     <t>1497: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM &gt; ETIOLOGY FIELD - (#63.05-12 &gt; 63.3-.01 &gt; 61.2-)</t>
   </si>
   <si>
@@ -1402,6 +1217,27 @@
   </si>
   <si>
     <t>Observation.value[x].text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2244,7 +2080,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AT77"/>
+  <dimension ref="A1:AR66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.69140625" customWidth="true" bestFit="true"/>
@@ -2290,8 +2126,6 @@
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
     <col min="43" max="43" width="217.01953125" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="57.953125" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="217.01953125" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="57.953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2427,12 +2261,6 @@
       <c r="AR1" t="s" s="1">
         <v>80</v>
       </c>
-      <c r="AS1" t="s" s="1">
-        <v>79</v>
-      </c>
-      <c r="AT1" t="s" s="1">
-        <v>80</v>
-      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -2559,12 +2387,6 @@
       <c r="AR2" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT2" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
@@ -2691,12 +2513,6 @@
       <c r="AR3" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS3" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT3" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
@@ -2821,12 +2637,6 @@
       <c r="AR4" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS4" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT4" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
@@ -2953,12 +2763,6 @@
       <c r="AR5" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS5" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT5" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
@@ -3085,12 +2889,6 @@
       <c r="AR6" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS6" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT6" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
@@ -3217,12 +3015,6 @@
       <c r="AR7" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT7" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
@@ -3349,12 +3141,6 @@
       <c r="AR8" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT8" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
@@ -3481,12 +3267,6 @@
       <c r="AR9" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT9" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
@@ -3615,12 +3395,6 @@
       <c r="AR10" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT10" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
@@ -3747,12 +3521,6 @@
       <c r="AR11" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT11" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
@@ -3877,12 +3645,6 @@
       <c r="AR12" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT12" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
@@ -4009,12 +3771,6 @@
       <c r="AR13" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT13" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
@@ -4143,12 +3899,6 @@
       <c r="AR14" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT14" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
@@ -4277,12 +4027,6 @@
       <c r="AR15" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT15" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
@@ -4411,12 +4155,6 @@
       <c r="AR16" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT16" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
@@ -4437,7 +4175,7 @@
         <v>94</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>84</v>
@@ -4541,12 +4279,6 @@
         <v>210</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS17" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AT17" t="s" s="2">
         <v>84</v>
       </c>
     </row>
@@ -4673,12 +4405,6 @@
       <c r="AR18" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT18" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
@@ -4805,12 +4531,6 @@
       <c r="AR19" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT19" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
@@ -4937,12 +4657,6 @@
       <c r="AR20" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT20" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
@@ -5069,12 +4783,6 @@
       <c r="AR21" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT21" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
@@ -5201,12 +4909,6 @@
       <c r="AR22" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT22" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
@@ -5333,33 +5035,29 @@
       <c r="AR23" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT23" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>265</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>84</v>
@@ -5368,16 +5066,20 @@
         <v>84</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>162</v>
+        <v>256</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
       </c>
@@ -5386,7 +5088,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>84</v>
+        <v>267</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5401,13 +5103,13 @@
         <v>84</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>84</v>
+        <v>260</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5425,19 +5127,19 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>164</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>84</v>
@@ -5449,10 +5151,10 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>165</v>
+        <v>263</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>84</v>
+        <v>264</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>84</v>
@@ -5461,55 +5163,51 @@
         <v>84</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT24" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>139</v>
+        <v>269</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>141</v>
+        <v>270</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>167</v>
+        <v>271</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
       </c>
@@ -5533,81 +5231,75 @@
         <v>84</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>84</v>
+        <v>274</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>84</v>
+        <v>275</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>171</v>
+        <v>268</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>84</v>
+        <v>276</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>84</v>
+        <v>277</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>165</v>
+        <v>279</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>84</v>
+        <v>281</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>84</v>
+        <v>282</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT25" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5615,13 +5307,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>84</v>
@@ -5630,19 +5322,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5691,13 +5383,13 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>84</v>
@@ -5706,19 +5398,19 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>84</v>
+        <v>289</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>84</v>
@@ -5727,21 +5419,15 @@
         <v>84</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT26" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5752,7 +5438,7 @@
         <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>84</v>
@@ -5761,18 +5447,20 @@
         <v>84</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>161</v>
+        <v>294</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>162</v>
+        <v>295</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5821,19 +5509,19 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>164</v>
+        <v>293</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>84</v>
@@ -5842,13 +5530,13 @@
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>165</v>
+        <v>298</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>84</v>
@@ -5857,32 +5545,26 @@
         <v>84</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT27" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>139</v>
+        <v>300</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>84</v>
@@ -5891,21 +5573,23 @@
         <v>84</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>140</v>
+        <v>301</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>141</v>
+        <v>302</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>167</v>
+        <v>303</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
       </c>
@@ -5941,46 +5625,46 @@
         <v>84</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>171</v>
+        <v>299</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>84</v>
+        <v>306</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>84</v>
+        <v>307</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>165</v>
+        <v>308</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>84</v>
+        <v>309</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>84</v>
@@ -5989,25 +5673,19 @@
         <v>84</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT28" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>84</v>
+        <v>311</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -6017,7 +5695,7 @@
         <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>84</v>
@@ -6026,19 +5704,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>108</v>
+        <v>312</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>279</v>
+        <v>313</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -6075,19 +5753,17 @@
         <v>84</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6096,25 +5772,25 @@
         <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>84</v>
+        <v>318</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>319</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>284</v>
+        <v>321</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>285</v>
+        <v>322</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>84</v>
+        <v>323</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>84</v>
@@ -6123,25 +5799,21 @@
         <v>84</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT29" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>311</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -6151,7 +5823,7 @@
         <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>84</v>
@@ -6160,18 +5832,20 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>161</v>
+        <v>326</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
       </c>
@@ -6219,7 +5893,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6228,48 +5902,42 @@
         <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>84</v>
+        <v>318</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>106</v>
+        <v>319</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>84</v>
+        <v>323</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>84</v>
+        <v>327</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT30" t="s" s="2">
-        <v>84</v>
+        <v>328</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6283,7 +5951,7 @@
         <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>84</v>
@@ -6292,18 +5960,18 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>114</v>
+        <v>330</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>294</v>
+        <v>331</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>84</v>
       </c>
@@ -6351,7 +6019,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6363,7 +6031,7 @@
         <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>298</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>84</v>
@@ -6372,36 +6040,30 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>299</v>
+        <v>334</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>84</v>
+        <v>336</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS31" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AT31" t="s" s="2">
-        <v>84</v>
+        <v>338</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6412,10 +6074,10 @@
         <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>84</v>
@@ -6424,17 +6086,17 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>161</v>
+        <v>219</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>340</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
+        <v>341</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>305</v>
+        <v>342</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6483,13 +6145,13 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>306</v>
+        <v>339</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>84</v>
@@ -6498,42 +6160,36 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>307</v>
+        <v>344</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>308</v>
+        <v>345</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>84</v>
+        <v>346</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>84</v>
+        <v>347</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT32" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>348</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>348</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6547,7 +6203,7 @@
         <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>84</v>
@@ -6556,19 +6212,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>310</v>
+        <v>349</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>312</v>
+        <v>351</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>313</v>
+        <v>352</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>314</v>
+        <v>353</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6605,19 +6261,17 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>315</v>
+        <v>348</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6626,50 +6280,46 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>84</v>
+        <v>354</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>106</v>
+        <v>355</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>84</v>
+        <v>356</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>316</v>
+        <v>357</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>317</v>
+        <v>358</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT33" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>360</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
       </c>
@@ -6681,7 +6331,7 @@
         <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>84</v>
@@ -6690,19 +6340,19 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6751,7 +6401,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6760,64 +6410,56 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>84</v>
+        <v>354</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>106</v>
+        <v>355</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>84</v>
+        <v>356</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>324</v>
+        <v>357</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>325</v>
+        <v>358</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT34" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>326</v>
+        <v>362</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>84</v>
@@ -6826,20 +6468,16 @@
         <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>256</v>
+        <v>162</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>84</v>
       </c>
@@ -6848,7 +6486,7 @@
         <v>84</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>328</v>
+        <v>84</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>84</v>
@@ -6863,13 +6501,13 @@
         <v>84</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>260</v>
+        <v>84</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>261</v>
+        <v>84</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>84</v>
@@ -6887,19 +6525,19 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>255</v>
+        <v>164</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>84</v>
@@ -6911,10 +6549,10 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>263</v>
+        <v>165</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>264</v>
+        <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>84</v>
@@ -6923,57 +6561,49 @@
         <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT35" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>364</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>329</v>
+        <v>365</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>330</v>
+        <v>139</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>331</v>
+        <v>141</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>332</v>
+        <v>167</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>84</v>
       </c>
@@ -6997,81 +6627,75 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>335</v>
+        <v>84</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>336</v>
+        <v>84</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>171</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>337</v>
+        <v>84</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>338</v>
+        <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>339</v>
+        <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>340</v>
+        <v>165</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>341</v>
+        <v>84</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>342</v>
+        <v>84</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS36" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AT36" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7079,10 +6703,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>95</v>
@@ -7094,19 +6718,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -7155,13 +6779,13 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>344</v>
+        <v>373</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>84</v>
@@ -7170,42 +6794,36 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>350</v>
+        <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>353</v>
+        <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AS37" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AT37" t="s" s="2">
-        <v>355</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7216,7 +6834,7 @@
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>84</v>
@@ -7228,18 +6846,20 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>357</v>
+        <v>161</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
       </c>
@@ -7287,13 +6907,13 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>84</v>
@@ -7308,13 +6928,13 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>339</v>
+        <v>384</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>353</v>
+        <v>84</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>84</v>
@@ -7323,25 +6943,19 @@
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT38" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>363</v>
+        <v>84</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7351,28 +6965,28 @@
         <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>364</v>
+        <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7397,13 +7011,11 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>84</v>
+        <v>391</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7421,7 +7033,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7430,25 +7042,25 @@
         <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>84</v>
+        <v>392</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>369</v>
+        <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>370</v>
+        <v>137</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>372</v>
+        <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>84</v>
@@ -7457,56 +7069,50 @@
         <v>84</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT39" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>375</v>
+        <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7531,92 +7137,86 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AC40" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>381</v>
+        <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>382</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>84</v>
+        <v>402</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>84</v>
+        <v>405</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT40" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>95</v>
@@ -7625,22 +7225,22 @@
         <v>84</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>376</v>
+        <v>408</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>377</v>
+        <v>409</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>378</v>
+        <v>410</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7689,57 +7289,51 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>381</v>
+        <v>84</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>382</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AS41" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AT41" t="s" s="2">
-        <v>391</v>
+        <v>415</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7759,19 +7353,19 @@
         <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>393</v>
+        <v>183</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>396</v>
+        <v>419</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7797,13 +7391,13 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>84</v>
+        <v>421</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>84</v>
+        <v>422</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -7821,7 +7415,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7839,39 +7433,33 @@
         <v>84</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>84</v>
+        <v>423</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>399</v>
+        <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>84</v>
+        <v>426</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>400</v>
+        <v>84</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AS42" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AT42" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7882,7 +7470,7 @@
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>84</v>
@@ -7891,20 +7479,22 @@
         <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>403</v>
+        <v>428</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7929,13 +7519,13 @@
         <v>84</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>84</v>
+        <v>432</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>84</v>
+        <v>433</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>84</v>
@@ -7953,13 +7543,13 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>84</v>
@@ -7968,42 +7558,36 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>406</v>
+        <v>84</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>409</v>
+        <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>410</v>
+        <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS43" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AT43" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8023,23 +7607,21 @@
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>414</v>
+        <v>439</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
@@ -8075,17 +7657,19 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AC44" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8094,52 +7678,44 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>417</v>
+        <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>418</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>84</v>
+        <v>445</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT44" t="s" s="2">
-        <v>84</v>
+        <v>446</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>423</v>
+        <v>447</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>84</v>
       </c>
@@ -8151,29 +7727,27 @@
         <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>183</v>
+        <v>448</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>413</v>
+        <v>449</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>84</v>
       </c>
@@ -8221,7 +7795,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8230,48 +7804,42 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>417</v>
+        <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>418</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>419</v>
+        <v>452</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>420</v>
+        <v>453</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>421</v>
+        <v>454</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>422</v>
+        <v>455</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT45" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>425</v>
+        <v>456</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>426</v>
+        <v>456</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8282,7 +7850,7 @@
         <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>84</v>
@@ -8294,16 +7862,20 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>161</v>
+        <v>457</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>162</v>
+        <v>458</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
@@ -8351,19 +7923,19 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>164</v>
+        <v>456</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>84</v>
@@ -8372,10 +7944,10 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>84</v>
+        <v>463</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>165</v>
+        <v>464</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -8387,32 +7959,26 @@
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT46" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>427</v>
+        <v>465</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>428</v>
+        <v>465</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>84</v>
@@ -8424,17 +7990,15 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8471,31 +8035,31 @@
         <v>84</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>84</v>
@@ -8519,25 +8083,19 @@
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT47" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>429</v>
+        <v>466</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>430</v>
+        <v>466</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8553,23 +8111,21 @@
         <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>269</v>
+        <v>141</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>270</v>
+        <v>167</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8617,7 +8173,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>273</v>
+        <v>171</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8629,7 +8185,7 @@
         <v>84</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>84</v>
@@ -8638,10 +8194,10 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>274</v>
+        <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>275</v>
+        <v>165</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
@@ -8650,59 +8206,53 @@
         <v>84</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>431</v>
+        <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS48" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AT48" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>432</v>
+        <v>467</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>433</v>
+        <v>467</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>84</v>
+        <v>468</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>319</v>
+        <v>469</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>320</v>
+        <v>470</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>321</v>
+        <v>143</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>322</v>
+        <v>149</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8751,19 +8301,19 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>323</v>
+        <v>471</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>84</v>
@@ -8772,10 +8322,10 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>324</v>
+        <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>325</v>
+        <v>137</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
@@ -8787,21 +8337,15 @@
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT49" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>434</v>
+        <v>472</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>434</v>
+        <v>472</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8815,7 +8359,7 @@
         <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>84</v>
@@ -8824,20 +8368,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>183</v>
+        <v>473</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>435</v>
+        <v>474</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8861,11 +8401,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>439</v>
+        <v>84</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8883,7 +8425,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>434</v>
+        <v>472</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8892,7 +8434,7 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -8904,10 +8446,10 @@
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>137</v>
+        <v>477</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>441</v>
+        <v>478</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -8919,32 +8461,26 @@
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT50" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>442</v>
+        <v>479</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>442</v>
+        <v>479</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>443</v>
+        <v>84</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>84</v>
@@ -8956,20 +8492,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>183</v>
+        <v>473</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>444</v>
+        <v>480</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>84</v>
       </c>
@@ -8993,13 +8525,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>448</v>
+        <v>84</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -9017,16 +8549,16 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>442</v>
+        <v>479</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>84</v>
+        <v>476</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>106</v>
@@ -9035,39 +8567,33 @@
         <v>84</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>450</v>
+        <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>453</v>
+        <v>84</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT51" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>454</v>
+        <v>483</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>454</v>
+        <v>483</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9078,7 +8604,7 @@
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>84</v>
@@ -9090,19 +8616,19 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>455</v>
+        <v>183</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>456</v>
+        <v>484</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>457</v>
+        <v>485</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>458</v>
+        <v>486</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>459</v>
+        <v>487</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -9127,13 +8653,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>84</v>
+        <v>488</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>84</v>
+        <v>489</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -9151,13 +8677,13 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>454</v>
+        <v>483</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>84</v>
@@ -9169,13 +8695,13 @@
         <v>84</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>84</v>
+        <v>490</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>461</v>
+        <v>404</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -9184,24 +8710,18 @@
         <v>84</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>462</v>
+        <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AS52" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AT52" t="s" s="2">
-        <v>463</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9212,7 +8732,7 @@
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>84</v>
@@ -9227,15 +8747,17 @@
         <v>183</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>466</v>
+        <v>494</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
@@ -9259,13 +8781,13 @@
         <v>84</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>468</v>
+        <v>420</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>469</v>
+        <v>497</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>470</v>
+        <v>498</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
@@ -9283,13 +8805,13 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>84</v>
@@ -9301,39 +8823,33 @@
         <v>84</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>473</v>
+        <v>404</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>474</v>
+        <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT53" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>475</v>
+        <v>499</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>475</v>
+        <v>499</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9356,19 +8872,17 @@
         <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>183</v>
+        <v>500</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>476</v>
+        <v>501</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>479</v>
+        <v>503</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9393,13 +8907,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>468</v>
+        <v>84</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>480</v>
+        <v>84</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>481</v>
+        <v>84</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9417,7 +8931,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>475</v>
+        <v>499</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9438,10 +8952,10 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>482</v>
+        <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
@@ -9453,21 +8967,15 @@
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT54" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9490,17 +8998,15 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>485</v>
+        <v>161</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9549,7 +9055,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9567,39 +9073,33 @@
         <v>84</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>489</v>
+        <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>492</v>
+        <v>84</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>493</v>
+        <v>84</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AS55" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AT55" t="s" s="2">
-        <v>494</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9610,7 +9110,7 @@
         <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>84</v>
@@ -9619,19 +9119,19 @@
         <v>84</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9681,13 +9181,13 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>84</v>
@@ -9699,39 +9199,33 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>500</v>
+        <v>84</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>503</v>
+        <v>84</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT56" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9751,23 +9245,21 @@
         <v>84</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>509</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>84</v>
       </c>
@@ -9815,7 +9307,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9827,7 +9319,7 @@
         <v>84</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>510</v>
+        <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>84</v>
@@ -9836,10 +9328,10 @@
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
@@ -9851,21 +9343,15 @@
         <v>84</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT57" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9876,7 +9362,7 @@
         <v>82</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>84</v>
@@ -9885,19 +9371,23 @@
         <v>84</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>161</v>
+        <v>457</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>162</v>
+        <v>523</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
       </c>
@@ -9945,19 +9435,19 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>164</v>
+        <v>522</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9966,10 +9456,10 @@
         <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>84</v>
+        <v>527</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>165</v>
+        <v>528</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
@@ -9981,32 +9471,26 @@
         <v>84</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT58" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>514</v>
+        <v>529</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>514</v>
+        <v>529</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>84</v>
@@ -10018,17 +9502,15 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10077,19 +9559,19 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>84</v>
@@ -10113,25 +9595,19 @@
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT59" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>516</v>
+        <v>139</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -10144,26 +9620,24 @@
         <v>84</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>517</v>
+        <v>141</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>518</v>
+        <v>167</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O60" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>84</v>
       </c>
@@ -10211,7 +9685,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>519</v>
+        <v>171</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10235,7 +9709,7 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
@@ -10247,53 +9721,51 @@
         <v>84</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT60" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>84</v>
+        <v>468</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>521</v>
+        <v>140</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>522</v>
+        <v>469</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>470</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
       </c>
@@ -10341,19 +9813,19 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>520</v>
+        <v>471</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>524</v>
+        <v>84</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>84</v>
@@ -10362,10 +9834,10 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>525</v>
+        <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>526</v>
+        <v>137</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -10377,21 +9849,15 @@
         <v>84</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT61" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10399,7 +9865,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>94</v>
@@ -10411,19 +9877,23 @@
         <v>84</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>521</v>
+        <v>183</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
       </c>
@@ -10447,13 +9917,13 @@
         <v>84</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>84</v>
+        <v>536</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>84</v>
+        <v>275</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
@@ -10471,16 +9941,16 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>524</v>
+        <v>84</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -10489,16 +9959,16 @@
         <v>84</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>84</v>
+        <v>537</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>525</v>
+        <v>278</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>530</v>
+        <v>279</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>84</v>
@@ -10507,21 +9977,15 @@
         <v>84</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT62" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10541,22 +10005,22 @@
         <v>84</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>183</v>
+        <v>349</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>535</v>
+        <v>353</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10581,13 +10045,13 @@
         <v>84</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>536</v>
+        <v>84</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>537</v>
+        <v>84</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>84</v>
@@ -10605,7 +10069,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10623,39 +10087,33 @@
         <v>84</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>539</v>
+        <v>357</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>452</v>
+        <v>358</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT63" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10666,7 +10124,7 @@
         <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>84</v>
@@ -10681,16 +10139,16 @@
         <v>183</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>544</v>
+        <v>390</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10715,13 +10173,13 @@
         <v>84</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>468</v>
+        <v>188</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>546</v>
+        <v>391</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10739,16 +10197,16 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>84</v>
+        <v>548</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>106</v>
@@ -10757,13 +10215,13 @@
         <v>84</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>538</v>
+        <v>84</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>539</v>
+        <v>137</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>452</v>
+        <v>393</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10775,32 +10233,26 @@
         <v>84</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT64" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>84</v>
+        <v>395</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>84</v>
@@ -10812,17 +10264,19 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>548</v>
+        <v>183</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>549</v>
+        <v>396</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="O65" t="s" s="2">
-        <v>551</v>
+        <v>399</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10847,13 +10301,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10871,13 +10325,13 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>84</v>
@@ -10889,39 +10343,33 @@
         <v>84</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>84</v>
+        <v>402</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>84</v>
+        <v>403</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>552</v>
+        <v>404</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>84</v>
+        <v>405</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT65" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10932,7 +10380,7 @@
         <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>84</v>
@@ -10944,16 +10392,20 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
       </c>
@@ -11001,13 +10453,13 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>84</v>
@@ -11022,10 +10474,10 @@
         <v>84</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>525</v>
+        <v>463</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>556</v>
+        <v>464</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
@@ -11037,1481 +10489,11 @@
         <v>84</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT66" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT67" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT68" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT69" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT70" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT71" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT72" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="P73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT73" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AQ74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT74" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT75" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT76" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT77" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT77">
+  <autoFilter ref="A1:AR66">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12521,7 +10503,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI76">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$65</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2701" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2660" uniqueCount="547">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -897,7 +897,65 @@
     <t>116680003 |Is a|</t>
   </si>
   <si>
-    <t>1480: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03) case Not NULL</t>
+    <t>Observation.code.id</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>1480: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case Not NULL</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1098,6 +1156,10 @@
     <t>Observation.performer</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+</t>
+  </si>
+  <si>
     <t>Who is responsible for the observation</t>
   </si>
   <si>
@@ -1119,7 +1181,7 @@
     <t>FiveWs.actor</t>
   </si>
   <si>
-    <t>1464: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (#63.05-.112)</t>
+    <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (#63.05-.04)</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -1161,85 +1223,6 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>Observation.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>1497: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM &gt; ETIOLOGY FIELD - (#63.05-12 &gt; 63.3-.01 &gt; 61.2-)</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>Observation.value[x].text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -1398,7 +1381,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologySpecimen)
+    <t xml:space="preserve">Reference(Specimen)
 </t>
   </si>
   <si>
@@ -2080,12 +2063,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR66"/>
+  <dimension ref="A1:AR65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.69140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2124,7 +2107,7 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="217.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="238.10546875" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="57.953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -5288,7 +5271,7 @@
         <v>281</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>282</v>
+        <v>84</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>84</v>
@@ -5296,10 +5279,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5307,35 +5290,31 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>285</v>
+        <v>162</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>84</v>
       </c>
@@ -5383,7 +5362,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>283</v>
+        <v>164</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5395,22 +5374,22 @@
         <v>84</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>289</v>
+        <v>84</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>290</v>
+        <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>291</v>
+        <v>165</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>292</v>
+        <v>84</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>84</v>
@@ -5424,14 +5403,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5447,19 +5426,19 @@
         <v>84</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>294</v>
+        <v>140</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>295</v>
+        <v>141</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>296</v>
+        <v>167</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>297</v>
+        <v>143</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5497,19 +5476,19 @@
         <v>84</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>293</v>
+        <v>171</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5521,7 +5500,7 @@
         <v>84</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>84</v>
@@ -5530,13 +5509,13 @@
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>298</v>
+        <v>165</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>292</v>
+        <v>84</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>84</v>
@@ -5550,24 +5529,24 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>300</v>
+        <v>84</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>84</v>
@@ -5576,19 +5555,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5637,13 +5616,13 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>84</v>
@@ -5652,25 +5631,25 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>306</v>
+        <v>84</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>309</v>
+        <v>84</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>84</v>
@@ -5678,14 +5657,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>311</v>
+        <v>84</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5695,7 +5674,7 @@
         <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>84</v>
@@ -5704,19 +5683,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>312</v>
+        <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5753,17 +5732,19 @@
         <v>84</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AC29" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5772,25 +5753,25 @@
         <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>318</v>
+        <v>84</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>319</v>
+        <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>320</v>
+        <v>84</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>321</v>
+        <v>300</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>323</v>
+        <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>84</v>
@@ -5804,20 +5785,18 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>311</v>
+        <v>84</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>94</v>
@@ -5832,19 +5811,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5893,7 +5872,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5902,42 +5881,42 @@
         <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>318</v>
+        <v>84</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>319</v>
+        <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>327</v>
+        <v>84</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>328</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5948,10 +5927,10 @@
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>84</v>
@@ -5960,16 +5939,16 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6019,13 +5998,13 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>84</v>
@@ -6040,44 +6019,44 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>334</v>
+        <v>278</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>337</v>
+        <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>338</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>84</v>
+        <v>319</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>84</v>
@@ -6086,17 +6065,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>219</v>
+        <v>320</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6145,13 +6126,13 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>84</v>
@@ -6160,25 +6141,25 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>347</v>
+        <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6186,14 +6167,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>84</v>
+        <v>330</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6212,19 +6193,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6261,7 +6242,7 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -6271,7 +6252,7 @@
         <v>170</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6280,28 +6261,28 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>84</v>
+        <v>339</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>356</v>
+        <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>84</v>
+        <v>342</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>359</v>
+        <v>84</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6312,16 +6293,16 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>84</v>
+        <v>330</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6340,19 +6321,19 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>183</v>
+        <v>345</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6401,7 +6382,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6410,42 +6391,42 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>84</v>
+        <v>339</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>356</v>
+        <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>84</v>
+        <v>342</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>359</v>
+        <v>84</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>84</v>
+        <v>346</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>84</v>
+        <v>347</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6459,24 +6440,26 @@
         <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>161</v>
+        <v>349</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>162</v>
+        <v>350</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6525,7 +6508,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>164</v>
+        <v>348</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6537,7 +6520,7 @@
         <v>84</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>84</v>
@@ -6546,34 +6529,34 @@
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>84</v>
+        <v>353</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>165</v>
+        <v>354</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>84</v>
+        <v>355</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>84</v>
+        <v>356</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6583,27 +6566,27 @@
         <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>140</v>
+        <v>359</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>141</v>
+        <v>360</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
       </c>
@@ -6639,19 +6622,19 @@
         <v>84</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>171</v>
+        <v>358</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6663,28 +6646,28 @@
         <v>84</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>84</v>
+        <v>363</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>84</v>
+        <v>364</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>84</v>
+        <v>366</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>84</v>
+        <v>367</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6692,10 +6675,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6706,7 +6689,7 @@
         <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>95</v>
@@ -6718,19 +6701,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6779,40 +6762,40 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>84</v>
+        <v>374</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>106</v>
+        <v>375</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>84</v>
+        <v>379</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>376</v>
+        <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -6820,10 +6803,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6837,28 +6820,28 @@
         <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6883,13 +6866,11 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>84</v>
+        <v>385</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6907,7 +6888,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6916,7 +6897,7 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>84</v>
+        <v>386</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6928,10 +6909,10 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>384</v>
+        <v>137</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>84</v>
@@ -6948,24 +6929,24 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>84</v>
+        <v>389</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>84</v>
@@ -6977,16 +6958,16 @@
         <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7013,9 +6994,11 @@
       <c r="X39" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Y39" s="2"/>
+      <c r="Y39" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7033,16 +7016,16 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>392</v>
+        <v>84</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>106</v>
@@ -7051,19 +7034,19 @@
         <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>84</v>
+        <v>396</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>137</v>
+        <v>397</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>84</v>
+        <v>399</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7074,14 +7057,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>395</v>
+        <v>84</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7091,7 +7074,7 @@
         <v>83</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>84</v>
@@ -7100,19 +7083,19 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>183</v>
+        <v>401</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7137,31 +7120,31 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7179,33 +7162,33 @@
         <v>84</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>402</v>
+        <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>405</v>
+        <v>84</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>84</v>
+        <v>408</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>84</v>
+        <v>409</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7216,10 +7199,10 @@
         <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>84</v>
@@ -7228,20 +7211,18 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>407</v>
+        <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>84</v>
       </c>
@@ -7265,13 +7246,13 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>84</v>
+        <v>414</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>84</v>
+        <v>415</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>84</v>
+        <v>416</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -7289,13 +7270,13 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>84</v>
@@ -7307,33 +7288,33 @@
         <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>84</v>
+        <v>417</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>414</v>
+        <v>84</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>415</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7359,15 +7340,17 @@
         <v>183</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7391,31 +7374,31 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7433,19 +7416,19 @@
         <v>84</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>423</v>
+        <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>426</v>
+        <v>84</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7456,10 +7439,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7473,7 +7456,7 @@
         <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>84</v>
@@ -7482,20 +7465,18 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>183</v>
+        <v>431</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>84</v>
       </c>
@@ -7519,13 +7500,13 @@
         <v>84</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>420</v>
+        <v>84</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>432</v>
+        <v>84</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>433</v>
+        <v>84</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>84</v>
@@ -7543,7 +7524,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7561,33 +7542,33 @@
         <v>84</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>84</v>
+        <v>435</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>84</v>
+        <v>438</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>84</v>
+        <v>439</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>84</v>
+        <v>440</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7601,7 +7582,7 @@
         <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>84</v>
@@ -7610,16 +7591,16 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7669,7 +7650,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7687,33 +7668,33 @@
         <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>445</v>
+        <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>446</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7724,7 +7705,7 @@
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>84</v>
@@ -7736,18 +7717,20 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
       </c>
@@ -7795,37 +7778,37 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>106</v>
+        <v>456</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>452</v>
+        <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>455</v>
+        <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7836,10 +7819,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7850,7 +7833,7 @@
         <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>84</v>
@@ -7862,20 +7845,16 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>457</v>
+        <v>161</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>458</v>
+        <v>162</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
@@ -7923,19 +7902,19 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>456</v>
+        <v>164</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>462</v>
+        <v>84</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>84</v>
@@ -7944,10 +7923,10 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>463</v>
+        <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>464</v>
+        <v>165</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -7964,21 +7943,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>84</v>
@@ -7990,15 +7969,17 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8047,19 +8028,19 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>84</v>
@@ -8088,14 +8069,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>139</v>
+        <v>462</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8108,24 +8089,26 @@
         <v>84</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>141</v>
+        <v>463</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>167</v>
+        <v>464</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8173,7 +8156,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>171</v>
+        <v>465</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8197,7 +8180,7 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
@@ -8214,46 +8197,42 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>468</v>
+        <v>84</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>140</v>
+        <v>467</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8301,31 +8280,31 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AG49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AN49" t="s" s="2">
-        <v>137</v>
+        <v>472</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
@@ -8342,10 +8321,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8368,7 +8347,7 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>474</v>
@@ -8425,7 +8404,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8434,7 +8413,7 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -8446,10 +8425,10 @@
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -8466,10 +8445,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8492,16 +8471,20 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>473</v>
+        <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>84</v>
       </c>
@@ -8525,13 +8508,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>84</v>
+        <v>482</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>84</v>
+        <v>483</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8549,7 +8532,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8558,7 +8541,7 @@
         <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>476</v>
+        <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>106</v>
@@ -8567,13 +8550,13 @@
         <v>84</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>84</v>
+        <v>484</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>482</v>
+        <v>398</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
@@ -8590,10 +8573,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8604,7 +8587,7 @@
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>84</v>
@@ -8619,16 +8602,16 @@
         <v>183</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8653,13 +8636,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>118</v>
+        <v>414</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -8677,13 +8660,13 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>84</v>
@@ -8695,13 +8678,13 @@
         <v>84</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -8718,10 +8701,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8732,7 +8715,7 @@
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>84</v>
@@ -8744,19 +8727,17 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>183</v>
+        <v>494</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -8781,13 +8762,13 @@
         <v>84</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>420</v>
+        <v>84</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>497</v>
+        <v>84</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>498</v>
+        <v>84</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
@@ -8805,13 +8786,13 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>84</v>
@@ -8823,13 +8804,13 @@
         <v>84</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>490</v>
+        <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>491</v>
+        <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>404</v>
+        <v>498</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -8872,18 +8853,16 @@
         <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>502</v>
-      </c>
       <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>503</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>84</v>
       </c>
@@ -8952,10 +8931,10 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>84</v>
+        <v>471</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
@@ -8972,10 +8951,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8986,7 +8965,7 @@
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>84</v>
@@ -8995,18 +8974,20 @@
         <v>84</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>161</v>
+        <v>504</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9055,13 +9036,13 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>84</v>
@@ -9076,10 +9057,10 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>477</v>
+        <v>508</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
@@ -9096,10 +9077,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9122,16 +9103,16 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9181,7 +9162,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9202,7 +9183,7 @@
         <v>84</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>515</v>
@@ -9248,18 +9229,20 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>84</v>
       </c>
@@ -9328,10 +9311,10 @@
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
@@ -9348,10 +9331,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9362,7 +9345,7 @@
         <v>82</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>84</v>
@@ -9371,23 +9354,19 @@
         <v>84</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>457</v>
+        <v>161</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>523</v>
+        <v>162</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>526</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>84</v>
       </c>
@@ -9435,19 +9414,19 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>522</v>
+        <v>164</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9456,10 +9435,10 @@
         <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>527</v>
+        <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>528</v>
+        <v>165</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
@@ -9476,21 +9455,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>84</v>
@@ -9502,15 +9481,17 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9559,19 +9540,19 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>84</v>
@@ -9600,14 +9581,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>139</v>
+        <v>462</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9620,24 +9601,26 @@
         <v>84</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>141</v>
+        <v>463</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>167</v>
+        <v>464</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
       </c>
@@ -9685,7 +9668,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>171</v>
+        <v>465</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9709,7 +9692,7 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
@@ -9726,45 +9709,45 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>468</v>
+        <v>84</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>469</v>
+        <v>527</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>470</v>
+        <v>528</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>143</v>
+        <v>529</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>149</v>
+        <v>273</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9789,13 +9772,13 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>84</v>
+        <v>414</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>84</v>
+        <v>530</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>84</v>
+        <v>275</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -9813,34 +9796,34 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>471</v>
+        <v>526</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>84</v>
+        <v>531</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>137</v>
+        <v>279</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>84</v>
@@ -9865,7 +9848,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>94</v>
@@ -9880,7 +9863,7 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>183</v>
+        <v>369</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>533</v>
@@ -9892,7 +9875,7 @@
         <v>535</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>273</v>
+        <v>373</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -9917,13 +9900,13 @@
         <v>84</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>420</v>
+        <v>84</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>536</v>
+        <v>84</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>275</v>
+        <v>84</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
@@ -9944,7 +9927,7 @@
         <v>532</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>94</v>
@@ -9959,19 +9942,19 @@
         <v>84</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>278</v>
+        <v>377</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>279</v>
+        <v>378</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>280</v>
+        <v>84</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>84</v>
+        <v>379</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -9982,10 +9965,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10005,22 +9988,22 @@
         <v>84</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>349</v>
+        <v>183</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="N63" t="s" s="2">
-        <v>541</v>
-      </c>
       <c r="O63" t="s" s="2">
-        <v>353</v>
+        <v>384</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10045,13 +10028,13 @@
         <v>84</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>84</v>
+        <v>541</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>84</v>
+        <v>385</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>84</v>
@@ -10069,7 +10052,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10078,7 +10061,7 @@
         <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>84</v>
+        <v>542</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>106</v>
@@ -10087,19 +10070,19 @@
         <v>84</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>542</v>
+        <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>357</v>
+        <v>137</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>359</v>
+        <v>84</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10117,14 +10100,14 @@
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>84</v>
+        <v>389</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>84</v>
@@ -10139,16 +10122,16 @@
         <v>183</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>544</v>
+        <v>390</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>545</v>
+        <v>391</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>546</v>
+        <v>392</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10176,10 +10159,10 @@
         <v>188</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>547</v>
+        <v>394</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10203,10 +10186,10 @@
         <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>548</v>
+        <v>84</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>106</v>
@@ -10215,19 +10198,19 @@
         <v>84</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>84</v>
+        <v>396</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>137</v>
+        <v>397</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>84</v>
+        <v>399</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10238,14 +10221,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>395</v>
+        <v>84</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10264,19 +10247,19 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>396</v>
+        <v>545</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>397</v>
+        <v>546</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>398</v>
+        <v>454</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>399</v>
+        <v>455</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10301,13 +10284,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>400</v>
+        <v>84</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10325,7 +10308,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10343,157 +10326,29 @@
         <v>84</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>402</v>
+        <v>84</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>403</v>
+        <v>457</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>404</v>
+        <v>458</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>405</v>
+        <v>84</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR65" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR66" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR66">
+  <autoFilter ref="A1:AR65">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10503,7 +10358,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI65">
+  <conditionalFormatting sqref="A2:AI64">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="596">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Abstract</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -828,28 +828,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:Laboratory</t>
-  </si>
-  <si>
-    <t>Laboratory</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -860,6 +838,31 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>843: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#laboratory</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:Laboratory</t>
+  </si>
+  <si>
+    <t>Laboratory</t>
+  </si>
+  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -1113,6 +1116,12 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1287,6 +1296,12 @@
   </si>
   <si>
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
+  </si>
+  <si>
+    <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.VerifyingStaffIEN</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -5060,7 +5075,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -5078,16 +5093,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5112,7 +5127,7 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>266</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
@@ -5127,10 +5142,10 @@
         <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5138,13 +5153,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>257</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -5188,7 +5203,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5206,10 +5221,10 @@
         <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5257,10 +5272,10 @@
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5268,14 +5283,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5297,16 +5312,16 @@
         <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5334,10 +5349,10 @@
         <v>188</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -5355,7 +5370,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>94</v>
@@ -5376,30 +5391,30 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5520,10 +5535,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5646,10 +5661,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5672,19 +5687,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5733,7 +5748,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5748,7 +5763,7 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -5760,10 +5775,10 @@
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5774,10 +5789,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5898,10 +5913,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6024,10 +6039,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6053,16 +6068,16 @@
         <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -6111,7 +6126,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6126,7 +6141,7 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
@@ -6138,10 +6153,10 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6152,10 +6167,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6181,13 +6196,13 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6237,7 +6252,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6264,10 +6279,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6278,10 +6293,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6307,14 +6322,14 @@
         <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6363,7 +6378,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6378,7 +6393,7 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
@@ -6390,10 +6405,10 @@
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6404,10 +6419,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6433,14 +6448,14 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6489,7 +6504,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6504,7 +6519,7 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>84</v>
@@ -6516,10 +6531,10 @@
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6530,10 +6545,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6556,19 +6571,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6617,7 +6632,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6644,10 +6659,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6658,10 +6673,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6687,16 +6702,16 @@
         <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6745,7 +6760,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6772,10 +6787,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6786,10 +6801,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6812,19 +6827,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6873,7 +6888,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6888,25 +6903,25 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>84</v>
+        <v>354</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>84</v>
+        <v>355</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -6914,10 +6929,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6940,16 +6955,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6999,7 +7014,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7026,13 +7041,13 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -7040,14 +7055,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7066,19 +7081,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7127,7 +7142,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7148,19 +7163,19 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7168,14 +7183,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7194,19 +7209,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7243,7 +7258,7 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7253,7 +7268,7 @@
         <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7262,10 +7277,10 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7274,19 +7289,19 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7294,16 +7309,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7322,19 +7337,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7383,7 +7398,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7392,31 +7407,31 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7424,10 +7439,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7450,16 +7465,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7509,7 +7524,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7524,10 +7539,10 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>84</v>
@@ -7536,13 +7551,13 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7550,10 +7565,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7567,7 +7582,7 @@
         <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>84</v>
@@ -7576,17 +7591,17 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7635,7 +7650,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7650,25 +7665,25 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>84</v>
+        <v>411</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>84</v>
+        <v>412</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -7676,10 +7691,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7702,19 +7717,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7763,7 +7778,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7772,10 +7787,10 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7787,27 +7802,27 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7833,16 +7848,16 @@
         <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7871,25 +7886,25 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7898,7 +7913,7 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7919,7 +7934,7 @@
         <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7930,14 +7945,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7959,16 +7974,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -7996,10 +8011,10 @@
         <v>188</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8017,7 +8032,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8041,27 +8056,27 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8084,19 +8099,19 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8145,7 +8160,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8160,10 +8175,10 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>84</v>
@@ -8172,10 +8187,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8186,10 +8201,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8215,13 +8230,13 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8247,31 +8262,31 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8295,27 +8310,27 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8341,16 +8356,16 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8375,31 +8390,31 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8426,10 +8441,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8440,10 +8455,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8466,16 +8481,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8525,7 +8540,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8540,36 +8555,36 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8592,16 +8607,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8651,7 +8666,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8675,27 +8690,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8718,19 +8733,19 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8779,7 +8794,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8791,7 +8806,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8806,10 +8821,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8820,10 +8835,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8944,10 +8959,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9070,14 +9085,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9099,10 +9114,10 @@
         <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>143</v>
@@ -9157,7 +9172,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9198,10 +9213,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9224,13 +9239,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9281,7 +9296,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9290,7 +9305,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9308,10 +9323,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9322,10 +9337,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9348,13 +9363,13 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9405,7 +9420,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9414,7 +9429,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9432,10 +9447,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9446,10 +9461,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9475,16 +9490,16 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9512,28 +9527,28 @@
         <v>118</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9557,13 +9572,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9574,10 +9589,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9603,16 +9618,16 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9637,31 +9652,31 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9685,13 +9700,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9702,10 +9717,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9728,17 +9743,17 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9787,7 +9802,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9817,7 +9832,7 @@
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9828,10 +9843,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9857,10 +9872,10 @@
         <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9911,7 +9926,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9938,10 +9953,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9952,10 +9967,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9978,16 +9993,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10037,7 +10052,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10064,10 +10079,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10078,10 +10093,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10104,16 +10119,16 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10163,7 +10178,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10190,10 +10205,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10204,10 +10219,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10230,19 +10245,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10291,7 +10306,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10318,10 +10333,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10332,10 +10347,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10456,10 +10471,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10582,14 +10597,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10611,10 +10626,10 @@
         <v>140</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>143</v>
@@ -10669,7 +10684,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10710,10 +10725,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10739,16 +10754,16 @@
         <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -10773,13 +10788,13 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -10797,7 +10812,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>94</v>
@@ -10821,16 +10836,16 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>84</v>
@@ -10838,10 +10853,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10864,19 +10879,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10925,7 +10940,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10949,27 +10964,27 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10995,16 +11010,16 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11032,10 +11047,10 @@
         <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11053,7 +11068,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11062,7 +11077,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -11083,7 +11098,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11094,14 +11109,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11123,16 +11138,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11160,10 +11175,10 @@
         <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11181,7 +11196,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11205,27 +11220,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11251,16 +11266,16 @@
         <v>85</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11309,7 +11324,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11336,10 +11351,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1100,7 +1100,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1285,7 +1285,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization|http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1513,7 +1513,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologySpecimen)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1100,7 +1100,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="597">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1376,6 +1376,9 @@
   <si>
     <t>obs-6
 us-core-2</t>
+  </si>
+  <si>
+    <t>null: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -7919,7 +7922,7 @@
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>84</v>
@@ -7934,7 +7937,7 @@
         <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7945,14 +7948,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7974,16 +7977,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8011,10 +8014,10 @@
         <v>188</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8032,7 +8035,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8056,27 +8059,27 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8099,19 +8102,19 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8160,7 +8163,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8175,10 +8178,10 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>84</v>
@@ -8187,10 +8190,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8201,10 +8204,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8230,13 +8233,13 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8262,13 +8265,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8286,7 +8289,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8310,27 +8313,27 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8356,16 +8359,16 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8390,13 +8393,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8414,7 +8417,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8441,10 +8444,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8455,10 +8458,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8481,16 +8484,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8540,7 +8543,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8555,36 +8558,36 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8607,16 +8610,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8666,7 +8669,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8690,27 +8693,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8733,19 +8736,19 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8794,7 +8797,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8806,7 +8809,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8821,10 +8824,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8835,10 +8838,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8959,10 +8962,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9085,14 +9088,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9114,10 +9117,10 @@
         <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>143</v>
@@ -9172,7 +9175,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9213,10 +9216,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9239,13 +9242,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9296,7 +9299,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9305,7 +9308,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9323,10 +9326,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9337,10 +9340,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9363,13 +9366,13 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9420,7 +9423,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9429,7 +9432,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9447,10 +9450,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9461,10 +9464,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9490,16 +9493,16 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9527,10 +9530,10 @@
         <v>118</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9548,7 +9551,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9572,13 +9575,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9589,10 +9592,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9618,16 +9621,16 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9652,13 +9655,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9676,7 +9679,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9700,13 +9703,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9717,10 +9720,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9743,17 +9746,17 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9802,7 +9805,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9832,7 +9835,7 @@
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9843,10 +9846,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9872,10 +9875,10 @@
         <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9926,7 +9929,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9953,10 +9956,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9967,10 +9970,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9993,16 +9996,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10052,7 +10055,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10079,10 +10082,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10093,10 +10096,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10119,16 +10122,16 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10178,7 +10181,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10205,10 +10208,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10219,10 +10222,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10245,19 +10248,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10306,7 +10309,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10333,10 +10336,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10347,10 +10350,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10471,10 +10474,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10597,14 +10600,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10626,10 +10629,10 @@
         <v>140</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>143</v>
@@ -10684,7 +10687,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10725,10 +10728,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10754,13 +10757,13 @@
         <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>276</v>
@@ -10788,10 +10791,10 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="Z68" t="s" s="2">
         <v>278</v>
@@ -10812,7 +10815,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>94</v>
@@ -10836,7 +10839,7 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>281</v>
@@ -10853,10 +10856,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10882,13 +10885,13 @@
         <v>418</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O69" t="s" s="2">
         <v>422</v>
@@ -10940,7 +10943,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10964,7 +10967,7 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>426</v>
@@ -10981,10 +10984,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11010,13 +11013,13 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O70" t="s" s="2">
         <v>433</v>
@@ -11047,7 +11050,7 @@
         <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>434</v>
@@ -11068,7 +11071,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11077,7 +11080,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -11098,7 +11101,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11109,14 +11112,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11138,16 +11141,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11175,10 +11178,10 @@
         <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11196,7 +11199,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11220,27 +11223,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11266,16 +11269,16 @@
         <v>85</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11324,7 +11327,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11351,10 +11354,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1378,7 +1378,7 @@
 us-core-2</t>
   </si>
   <si>
-    <t>null: target not supported</t>
+    <t>2031: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="598">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -965,6 +965,10 @@
   </si>
   <si>
     <t>Coding.system</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+LabObservationMicrobiologyObservation-1480-1:if Not NULL then fixed value http://loinc.org {null}</t>
   </si>
   <si>
     <t>1480-1: fixed value = http://loinc.org case Not NULL</t>
@@ -6141,10 +6145,10 @@
         <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>305</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
@@ -6156,10 +6160,10 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6170,10 +6174,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6199,13 +6203,13 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6255,7 +6259,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6282,10 +6286,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6296,10 +6300,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6325,14 +6329,14 @@
         <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6381,7 +6385,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6396,7 +6400,7 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
@@ -6408,10 +6412,10 @@
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6422,10 +6426,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6451,14 +6455,14 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6507,7 +6511,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6522,7 +6526,7 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>84</v>
@@ -6534,10 +6538,10 @@
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6548,10 +6552,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6574,19 +6578,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6635,7 +6639,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6662,10 +6666,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6676,10 +6680,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6705,16 +6709,16 @@
         <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6763,7 +6767,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6790,10 +6794,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6804,10 +6808,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6830,19 +6834,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6891,7 +6895,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6906,25 +6910,25 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -6932,10 +6936,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6958,16 +6962,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7017,7 +7021,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7047,10 +7051,10 @@
         <v>281</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -7058,14 +7062,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7084,19 +7088,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7145,7 +7149,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7166,19 +7170,19 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7186,14 +7190,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7212,19 +7216,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7261,7 +7265,7 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7271,7 +7275,7 @@
         <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7280,10 +7284,10 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7292,19 +7296,19 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7312,16 +7316,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7340,19 +7344,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7401,7 +7405,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7410,31 +7414,31 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7442,10 +7446,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7468,16 +7472,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7527,7 +7531,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7542,10 +7546,10 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>84</v>
@@ -7554,13 +7558,13 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7568,10 +7572,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7594,17 +7598,17 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7653,7 +7657,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7668,25 +7672,25 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -7694,10 +7698,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7720,19 +7724,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7781,7 +7785,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7790,10 +7794,10 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7805,27 +7809,27 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7851,16 +7855,16 @@
         <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7889,7 +7893,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7907,7 +7911,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7916,13 +7920,13 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>84</v>
@@ -7937,7 +7941,7 @@
         <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7948,14 +7952,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7977,16 +7981,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8014,10 +8018,10 @@
         <v>188</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8035,7 +8039,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8059,27 +8063,27 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8102,19 +8106,19 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8163,7 +8167,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8178,10 +8182,10 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>84</v>
@@ -8190,10 +8194,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8204,10 +8208,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8233,13 +8237,13 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8265,13 +8269,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8289,7 +8293,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8313,27 +8317,27 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8359,16 +8363,16 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8393,13 +8397,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8417,7 +8421,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8444,10 +8448,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8458,10 +8462,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8484,16 +8488,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8543,7 +8547,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8558,36 +8562,36 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8610,16 +8614,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8669,7 +8673,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8693,27 +8697,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8736,19 +8740,19 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8797,7 +8801,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8809,7 +8813,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8824,10 +8828,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8838,10 +8842,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8962,10 +8966,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9088,14 +9092,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9117,10 +9121,10 @@
         <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>143</v>
@@ -9175,7 +9179,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9216,10 +9220,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9242,13 +9246,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9299,7 +9303,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9308,7 +9312,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9326,10 +9330,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9340,10 +9344,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9366,13 +9370,13 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9423,7 +9427,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9432,7 +9436,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9450,10 +9454,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9464,10 +9468,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9493,16 +9497,16 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9530,10 +9534,10 @@
         <v>118</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9551,7 +9555,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9575,13 +9579,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9592,10 +9596,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9621,16 +9625,16 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9655,13 +9659,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9679,7 +9683,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9703,13 +9707,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9720,10 +9724,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9746,17 +9750,17 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9805,7 +9809,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9835,7 +9839,7 @@
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9846,10 +9850,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9875,10 +9879,10 @@
         <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9929,7 +9933,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9956,10 +9960,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9970,10 +9974,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9996,16 +10000,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10055,7 +10059,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10082,10 +10086,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10096,10 +10100,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10122,16 +10126,16 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10181,7 +10185,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10208,10 +10212,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10222,10 +10226,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10248,19 +10252,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10309,7 +10313,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10336,10 +10340,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10350,10 +10354,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10474,10 +10478,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10600,14 +10604,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10629,10 +10633,10 @@
         <v>140</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>143</v>
@@ -10687,7 +10691,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10728,10 +10732,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10757,13 +10761,13 @@
         <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>276</v>
@@ -10791,10 +10795,10 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Z68" t="s" s="2">
         <v>278</v>
@@ -10815,7 +10819,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>94</v>
@@ -10839,7 +10843,7 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>281</v>
@@ -10856,10 +10860,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10882,19 +10886,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10943,7 +10947,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10967,27 +10971,27 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11013,16 +11017,16 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11050,10 +11054,10 @@
         <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11071,7 +11075,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11080,7 +11084,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -11101,7 +11105,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11112,14 +11116,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11141,16 +11145,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11178,10 +11182,10 @@
         <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11199,7 +11203,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11223,27 +11227,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11269,16 +11273,16 @@
         <v>85</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11327,7 +11331,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11354,10 +11358,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -968,7 +968,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-LabObservationMicrobiologyObservation-1480-1:if Not NULL then fixed value http://loinc.org {null}</t>
+lomo-37-1480-1:undefined: if Not NULL then http://loinc.org {null}</t>
   </si>
   <si>
     <t>1480-1: fixed value = http://loinc.org case Not NULL</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1129,7 +1129,8 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn</t>
+    <t>demographics.lrdfn
+accession.collected</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -2249,7 +2249,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="250.93359375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3013" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3013" uniqueCount="603">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1129,8 +1129,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn
-accession.collected</t>
+    <t>Patient.PatientExtension.VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1284,6 +1283,9 @@
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
   </si>
   <si>
+    <t>Documents.ToTime,LabOrder.Result.ResultTime</t>
+  </si>
+  <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
@@ -1315,6 +1317,9 @@
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
   </si>
   <si>
+    <t>Documents.Clinician,Documents.DocumentExtension.CareProviders,LabOrder.Result.VerifiedBy</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1544,6 +1549,9 @@
   </si>
   <si>
     <t>Micro.Microbiology.MicrobiologyAccession</t>
+  </si>
+  <si>
+    <t>LabOrder.ResultExtension.GroupName</t>
   </si>
   <si>
     <t>&lt; 123038009 |Specimen|</t>
@@ -2249,7 +2257,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="250.93359375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="88.89453125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
@@ -7683,7 +7691,7 @@
         <v>405</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>85</v>
+        <v>406</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>85</v>
@@ -7692,13 +7700,13 @@
         <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>85</v>
@@ -7706,10 +7714,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7732,17 +7740,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -7791,7 +7799,7 @@
         <v>85</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7806,28 +7814,28 @@
         <v>107</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>85</v>
+        <v>417</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -7835,10 +7843,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7861,19 +7869,19 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -7922,7 +7930,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7931,10 +7939,10 @@
         <v>95</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>85</v>
@@ -7949,27 +7957,27 @@
         <v>85</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS44" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7995,16 +8003,16 @@
         <v>184</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8033,7 +8041,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>85</v>
@@ -8051,7 +8059,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8060,13 +8068,13 @@
         <v>95</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>85</v>
@@ -8084,7 +8092,7 @@
         <v>138</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>85</v>
@@ -8095,14 +8103,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -8124,16 +8132,16 @@
         <v>184</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8161,10 +8169,10 @@
         <v>189</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>85</v>
@@ -8182,7 +8190,7 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8209,27 +8217,27 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8252,19 +8260,19 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8313,7 +8321,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8328,10 +8336,10 @@
         <v>107</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>85</v>
@@ -8343,10 +8351,10 @@
         <v>85</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
@@ -8357,10 +8365,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8386,13 +8394,13 @@
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8418,13 +8426,13 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8442,7 +8450,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8469,27 +8477,27 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8515,16 +8523,16 @@
         <v>184</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8549,13 +8557,13 @@
         <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -8573,7 +8581,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8603,10 +8611,10 @@
         <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -8617,10 +8625,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8643,16 +8651,16 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8702,7 +8710,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8717,39 +8725,39 @@
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS50" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8772,16 +8780,16 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8831,7 +8839,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8858,27 +8866,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8901,19 +8909,19 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -8962,7 +8970,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -8974,7 +8982,7 @@
         <v>85</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>85</v>
@@ -8992,10 +9000,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -9006,10 +9014,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9133,10 +9141,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9262,14 +9270,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9291,10 +9299,10 @@
         <v>141</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>144</v>
@@ -9349,7 +9357,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9393,10 +9401,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9419,13 +9427,13 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9476,7 +9484,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9485,7 +9493,7 @@
         <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>107</v>
@@ -9506,10 +9514,10 @@
         <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
@@ -9520,10 +9528,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9546,13 +9554,13 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9603,7 +9611,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9612,7 +9620,7 @@
         <v>95</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>107</v>
@@ -9633,10 +9641,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9647,10 +9655,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9676,16 +9684,16 @@
         <v>184</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>85</v>
@@ -9713,10 +9721,10 @@
         <v>119</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>85</v>
@@ -9734,7 +9742,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9761,13 +9769,13 @@
         <v>85</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9778,10 +9786,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9807,16 +9815,16 @@
         <v>184</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -9841,13 +9849,13 @@
         <v>85</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>85</v>
@@ -9865,7 +9873,7 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9892,13 +9900,13 @@
         <v>85</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -9909,10 +9917,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9935,17 +9943,17 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
@@ -9994,7 +10002,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10027,7 +10035,7 @@
         <v>85</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10038,10 +10046,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10067,10 +10075,10 @@
         <v>162</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10121,7 +10129,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10151,10 +10159,10 @@
         <v>85</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10165,10 +10173,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10191,16 +10199,16 @@
         <v>96</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10250,7 +10258,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10280,10 +10288,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10294,10 +10302,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10320,16 +10328,16 @@
         <v>96</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10379,7 +10387,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10409,10 +10417,10 @@
         <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10423,10 +10431,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10449,19 +10457,19 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
@@ -10510,7 +10518,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10540,10 +10548,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10554,10 +10562,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10681,10 +10689,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10810,14 +10818,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10839,10 +10847,10 @@
         <v>141</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>144</v>
@@ -10897,7 +10905,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -10941,10 +10949,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10970,13 +10978,13 @@
         <v>184</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>277</v>
@@ -11004,10 +11012,10 @@
         <v>85</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="Z68" t="s" s="2">
         <v>279</v>
@@ -11028,7 +11036,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>95</v>
@@ -11055,7 +11063,7 @@
         <v>85</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>282</v>
@@ -11072,10 +11080,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11098,19 +11106,19 @@
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11159,7 +11167,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11186,27 +11194,27 @@
         <v>85</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS69" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11232,16 +11240,16 @@
         <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
@@ -11269,10 +11277,10 @@
         <v>189</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
@@ -11290,7 +11298,7 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11299,7 +11307,7 @@
         <v>95</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>107</v>
@@ -11323,7 +11331,7 @@
         <v>138</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
@@ -11334,14 +11342,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11363,16 +11371,16 @@
         <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11400,10 +11408,10 @@
         <v>189</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
@@ -11421,7 +11429,7 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11448,27 +11456,27 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11494,16 +11502,16 @@
         <v>86</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11552,7 +11560,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -11582,10 +11590,10 @@
         <v>85</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1129,7 +1129,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>Patient.PatientExtension.VeteranLrdfn</t>
+    <t>Patient.Extension[PatientExtension].VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1317,7 +1317,7 @@
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
   </si>
   <si>
-    <t>Documents.Clinician,Documents.DocumentExtension.CareProviders,LabOrder.Result.VerifiedBy</t>
+    <t>Documents.Clinician,Documents.Extension[DocumentExtension].CareProviders,LabOrder.Result.VerifiedBy</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1551,7 +1551,7 @@
     <t>Micro.Microbiology.MicrobiologyAccession</t>
   </si>
   <si>
-    <t>LabOrder.ResultExtension.GroupName</t>
+    <t>LabOrder.Extension[ResultExtension].GroupName</t>
   </si>
   <si>
     <t>&lt; 123038009 |Specimen|</t>
@@ -2257,7 +2257,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="250.93359375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="88.89453125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="99.32421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$74</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3013" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3096" uniqueCount="612">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-observation-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-observation-lab.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1298,7 +1298,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization|http://va.gov/fhir/StructureDefinition/Practitioner)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1311,6 +1311,47 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
+  </si>
+  <si>
+    <t>participation[typeCode=PRF]</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Observation.performer:va-at</t>
+  </si>
+  <si>
+    <t>va-at</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization)
+</t>
+  </si>
+  <si>
+    <t>1464: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.AccessioningInstitutionIEN</t>
+  </si>
+  <si>
+    <t>Documents.EnteredAt,LabOrder.Result.EnteredAt</t>
+  </si>
+  <si>
+    <t>Observation.performer:va-by</t>
+  </si>
+  <si>
+    <t>va-by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
+</t>
+  </si>
+  <si>
     <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
   </si>
   <si>
@@ -1318,18 +1359,6 @@
   </si>
   <si>
     <t>Documents.Clinician,Documents.Extension[DocumentExtension].CareProviders,LabOrder.Result.VerifiedBy</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
-  </si>
-  <si>
-    <t>participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -2217,7 +2246,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS72"/>
+  <dimension ref="A1:AS74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -7731,7 +7760,7 @@
         <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>85</v>
@@ -7787,16 +7816,14 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>410</v>
@@ -7814,28 +7841,28 @@
         <v>107</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AQ43" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AR43" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AR43" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -7843,12 +7870,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
       </c>
@@ -7869,19 +7898,17 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -7930,56 +7957,58 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK44" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AG44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="AL44" t="s" s="2">
-        <v>85</v>
+        <v>423</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>85</v>
+        <v>424</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>85</v>
+        <v>415</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>430</v>
+        <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>85</v>
+        <v>418</v>
       </c>
       <c r="AS44" t="s" s="2">
-        <v>433</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
       </c>
@@ -7997,22 +8026,20 @@
         <v>85</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>184</v>
+        <v>427</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8037,11 +8064,13 @@
         <v>85</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z45" t="s" s="2">
-        <v>439</v>
+        <v>85</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>85</v>
@@ -8059,43 +8088,43 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>440</v>
+        <v>85</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>85</v>
+        <v>429</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>85</v>
+        <v>430</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>85</v>
+        <v>415</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>138</v>
+        <v>416</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>85</v>
+        <v>418</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>85</v>
@@ -8103,45 +8132,45 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>444</v>
+        <v>85</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>184</v>
+        <v>432</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8166,13 +8195,13 @@
         <v>85</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>449</v>
+        <v>85</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>450</v>
+        <v>85</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>85</v>
@@ -8190,19 +8219,19 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>85</v>
+        <v>437</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>107</v>
+        <v>438</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8217,27 +8246,27 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>454</v>
+        <v>442</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8248,7 +8277,7 @@
         <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>96</v>
@@ -8260,19 +8289,19 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>456</v>
+        <v>184</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8297,13 +8326,11 @@
         <v>85</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>85</v>
+        <v>448</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>85</v>
@@ -8321,25 +8348,25 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>85</v>
+        <v>449</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>462</v>
+        <v>85</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>85</v>
@@ -8351,10 +8378,10 @@
         <v>85</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>463</v>
+        <v>138</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
@@ -8365,21 +8392,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>85</v>
+        <v>453</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>85</v>
@@ -8394,15 +8421,17 @@
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
       </c>
@@ -8426,13 +8455,13 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>469</v>
+        <v>189</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8450,13 +8479,13 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>85</v>
@@ -8477,27 +8506,27 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>475</v>
+        <v>463</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8508,10 +8537,10 @@
         <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>85</v>
@@ -8520,19 +8549,19 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>184</v>
+        <v>465</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8557,13 +8586,13 @@
         <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>469</v>
+        <v>85</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>481</v>
+        <v>85</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>482</v>
+        <v>85</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -8581,13 +8610,13 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>85</v>
@@ -8596,10 +8625,10 @@
         <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>85</v>
+        <v>470</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>85</v>
+        <v>471</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>85</v>
@@ -8611,10 +8640,10 @@
         <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -8625,10 +8654,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8642,7 +8671,7 @@
         <v>95</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>85</v>
@@ -8651,16 +8680,16 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>486</v>
+        <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8686,13 +8715,13 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>85</v>
+        <v>478</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>85</v>
+        <v>479</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>85</v>
+        <v>480</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8710,7 +8739,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8725,39 +8754,39 @@
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>490</v>
+        <v>85</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>491</v>
+        <v>85</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>492</v>
+        <v>85</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS50" t="s" s="2">
-        <v>496</v>
+        <v>484</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8780,18 +8809,20 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>498</v>
+        <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
       </c>
@@ -8815,13 +8846,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>85</v>
+        <v>478</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>85</v>
+        <v>490</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>85</v>
+        <v>491</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8839,7 +8870,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8866,27 +8897,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>502</v>
+        <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>505</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8897,10 +8928,10 @@
         <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>85</v>
@@ -8909,20 +8940,18 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>511</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>85</v>
       </c>
@@ -8970,54 +8999,54 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>512</v>
+        <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>85</v>
+        <v>499</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>85</v>
+        <v>501</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>85</v>
+        <v>502</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS52" t="s" s="2">
-        <v>85</v>
+        <v>505</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9040,15 +9069,17 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>162</v>
+        <v>507</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>163</v>
+        <v>508</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>85</v>
@@ -9097,7 +9128,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>165</v>
+        <v>506</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9109,7 +9140,7 @@
         <v>85</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>85</v>
@@ -9124,31 +9155,31 @@
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>85</v>
+        <v>511</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>85</v>
+        <v>512</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>166</v>
+        <v>513</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>85</v>
+        <v>514</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9167,18 +9198,20 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>141</v>
+        <v>516</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>142</v>
+        <v>517</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>168</v>
+        <v>518</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
       </c>
@@ -9226,7 +9259,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>172</v>
+        <v>515</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9238,7 +9271,7 @@
         <v>85</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>146</v>
+        <v>521</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>85</v>
@@ -9256,10 +9289,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>85</v>
+        <v>522</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>166</v>
+        <v>523</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9270,46 +9303,42 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>518</v>
+        <v>85</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>519</v>
+        <v>163</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>85</v>
       </c>
@@ -9357,19 +9386,19 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>521</v>
+        <v>165</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>85</v>
@@ -9390,7 +9419,7 @@
         <v>85</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
@@ -9401,21 +9430,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>85</v>
@@ -9427,15 +9456,17 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>523</v>
+        <v>141</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>524</v>
+        <v>142</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>85</v>
@@ -9484,19 +9515,19 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>522</v>
+        <v>172</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>526</v>
+        <v>85</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>85</v>
@@ -9514,10 +9545,10 @@
         <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>527</v>
+        <v>85</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>528</v>
+        <v>166</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
@@ -9528,42 +9559,46 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>85</v>
+        <v>527</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>523</v>
+        <v>141</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>529</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
       </c>
@@ -9611,19 +9646,19 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>526</v>
+        <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9641,10 +9676,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>527</v>
+        <v>85</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>532</v>
+        <v>138</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9655,10 +9690,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9681,20 +9716,16 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>184</v>
+        <v>532</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>537</v>
-      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>85</v>
       </c>
@@ -9718,13 +9749,13 @@
         <v>85</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>538</v>
+        <v>85</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>539</v>
+        <v>85</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>85</v>
@@ -9742,7 +9773,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9751,7 +9782,7 @@
         <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>85</v>
+        <v>535</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>107</v>
@@ -9769,13 +9800,13 @@
         <v>85</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>540</v>
+        <v>85</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>453</v>
+        <v>537</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9786,10 +9817,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9800,7 +9831,7 @@
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>85</v>
@@ -9812,20 +9843,16 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>184</v>
+        <v>532</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>546</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>85</v>
       </c>
@@ -9849,13 +9876,13 @@
         <v>85</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>469</v>
+        <v>85</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>547</v>
+        <v>85</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>548</v>
+        <v>85</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>85</v>
@@ -9873,16 +9900,16 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>85</v>
+        <v>535</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>107</v>
@@ -9900,13 +9927,13 @@
         <v>85</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>540</v>
+        <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -9917,10 +9944,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9943,17 +9970,19 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>550</v>
+        <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>544</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="O60" t="s" s="2">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
@@ -9978,13 +10007,13 @@
         <v>85</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>85</v>
+        <v>547</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>85</v>
+        <v>548</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>85</v>
@@ -10002,7 +10031,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10029,13 +10058,13 @@
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>85</v>
+        <v>549</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>85</v>
+        <v>550</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>554</v>
+        <v>462</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10046,10 +10075,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10060,7 +10089,7 @@
         <v>83</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>85</v>
@@ -10072,16 +10101,20 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>555</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
       </c>
@@ -10105,13 +10138,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>85</v>
+        <v>478</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>85</v>
+        <v>556</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>85</v>
+        <v>557</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10129,13 +10162,13 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>85</v>
@@ -10156,13 +10189,13 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>85</v>
+        <v>549</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>527</v>
+        <v>550</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>558</v>
+        <v>462</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10173,10 +10206,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10187,7 +10220,7 @@
         <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>85</v>
@@ -10196,21 +10229,21 @@
         <v>85</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="N62" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>85</v>
       </c>
@@ -10258,13 +10291,13 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>85</v>
@@ -10288,10 +10321,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>564</v>
+        <v>85</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10302,10 +10335,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10316,7 +10349,7 @@
         <v>83</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>85</v>
@@ -10325,20 +10358,18 @@
         <v>85</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>567</v>
+        <v>162</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>570</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10387,13 +10418,13 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>85</v>
@@ -10417,10 +10448,10 @@
         <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>564</v>
+        <v>536</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10431,10 +10462,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10457,20 +10488,18 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>507</v>
+        <v>569</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>576</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>85</v>
       </c>
@@ -10518,7 +10547,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10548,10 +10577,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10562,10 +10591,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10576,7 +10605,7 @@
         <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>85</v>
@@ -10585,18 +10614,20 @@
         <v>85</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>162</v>
+        <v>576</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>163</v>
+        <v>577</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>578</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>85</v>
@@ -10645,19 +10676,19 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>165</v>
+        <v>575</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>85</v>
@@ -10675,10 +10706,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>85</v>
+        <v>573</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>166</v>
+        <v>580</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10689,14 +10720,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10712,21 +10743,23 @@
         <v>85</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>141</v>
+        <v>516</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>142</v>
+        <v>582</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>168</v>
+        <v>583</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>585</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>85</v>
       </c>
@@ -10774,7 +10807,7 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>172</v>
+        <v>581</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -10786,7 +10819,7 @@
         <v>85</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>85</v>
@@ -10804,10 +10837,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>85</v>
+        <v>586</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>166</v>
+        <v>587</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -10818,46 +10851,42 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>518</v>
+        <v>85</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>519</v>
+        <v>163</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>85</v>
       </c>
@@ -10905,19 +10934,19 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>521</v>
+        <v>165</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>85</v>
@@ -10938,7 +10967,7 @@
         <v>85</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -10949,21 +10978,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>85</v>
@@ -10972,23 +11001,21 @@
         <v>85</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>583</v>
+        <v>142</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>584</v>
+        <v>168</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>85</v>
       </c>
@@ -11012,13 +11039,13 @@
         <v>85</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>469</v>
+        <v>85</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>586</v>
+        <v>85</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>279</v>
+        <v>85</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>85</v>
@@ -11036,19 +11063,19 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>582</v>
+        <v>172</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>85</v>
@@ -11063,16 +11090,16 @@
         <v>85</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>587</v>
+        <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>282</v>
+        <v>85</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>283</v>
+        <v>166</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>284</v>
+        <v>85</v>
       </c>
       <c r="AS68" t="s" s="2">
         <v>85</v>
@@ -11080,45 +11107,45 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>85</v>
+        <v>527</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>423</v>
+        <v>141</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>589</v>
+        <v>528</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>590</v>
+        <v>529</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>591</v>
+        <v>144</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>427</v>
+        <v>150</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11167,19 +11194,19 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>588</v>
+        <v>530</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>85</v>
@@ -11194,27 +11221,27 @@
         <v>85</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>592</v>
+        <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>431</v>
+        <v>85</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>432</v>
+        <v>138</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS69" t="s" s="2">
-        <v>433</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11222,7 +11249,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>95</v>
@@ -11234,22 +11261,22 @@
         <v>85</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>596</v>
-      </c>
       <c r="O70" t="s" s="2">
-        <v>438</v>
+        <v>277</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
@@ -11274,13 +11301,13 @@
         <v>85</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>189</v>
+        <v>478</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>439</v>
+        <v>279</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
@@ -11298,16 +11325,16 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>598</v>
+        <v>85</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>107</v>
@@ -11325,16 +11352,16 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>85</v>
+        <v>596</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>138</v>
+        <v>282</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>442</v>
+        <v>283</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>85</v>
+        <v>284</v>
       </c>
       <c r="AS70" t="s" s="2">
         <v>85</v>
@@ -11342,21 +11369,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>444</v>
+        <v>85</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>85</v>
@@ -11365,22 +11392,22 @@
         <v>85</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>184</v>
+        <v>432</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>445</v>
+        <v>598</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>446</v>
+        <v>599</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>447</v>
+        <v>600</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11405,13 +11432,13 @@
         <v>85</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>449</v>
+        <v>85</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>450</v>
+        <v>85</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
@@ -11429,13 +11456,13 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>85</v>
@@ -11456,27 +11483,27 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>451</v>
+        <v>601</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>454</v>
+        <v>442</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11487,7 +11514,7 @@
         <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>85</v>
@@ -11499,19 +11526,19 @@
         <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>86</v>
+        <v>184</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>510</v>
+        <v>605</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>511</v>
+        <v>447</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11536,13 +11563,13 @@
         <v>85</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>85</v>
+        <v>606</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>85</v>
+        <v>448</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>85</v>
@@ -11560,16 +11587,16 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>85</v>
+        <v>607</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>107</v>
@@ -11590,20 +11617,282 @@
         <v>85</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>513</v>
+        <v>138</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>514</v>
+        <v>451</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS72" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AR73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS73" t="s" s="2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AR74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS74" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS72">
+  <autoFilter ref="A1:AS74">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11613,7 +11902,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI71">
+  <conditionalFormatting sqref="A2:AI73">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3096" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3096" uniqueCount="613">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1309,6 +1309,10 @@
   </si>
   <si>
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -7816,7 +7820,7 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>266</v>
+        <v>415</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7850,19 +7854,19 @@
         <v>85</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -7870,13 +7874,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>410</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
@@ -7898,7 +7902,7 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>412</v>
@@ -7972,28 +7976,28 @@
         <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>85</v>
@@ -8001,13 +8005,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>410</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8029,7 +8033,7 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>412</v>
@@ -8103,28 +8107,28 @@
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>85</v>
@@ -8132,10 +8136,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8158,19 +8162,19 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8219,7 +8223,7 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8228,10 +8232,10 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8246,27 +8250,27 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8292,16 +8296,16 @@
         <v>184</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8330,7 +8334,7 @@
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>85</v>
@@ -8348,7 +8352,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8357,13 +8361,13 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>85</v>
@@ -8381,7 +8385,7 @@
         <v>138</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
@@ -8392,14 +8396,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8421,16 +8425,16 @@
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8458,10 +8462,10 @@
         <v>189</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8479,7 +8483,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8506,27 +8510,27 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8549,19 +8553,19 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8610,7 +8614,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8625,10 +8629,10 @@
         <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>85</v>
@@ -8640,10 +8644,10 @@
         <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -8654,10 +8658,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8683,13 +8687,13 @@
         <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8715,13 +8719,13 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8739,7 +8743,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8766,27 +8770,27 @@
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS50" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8812,16 +8816,16 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -8846,13 +8850,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8870,7 +8874,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8900,10 +8904,10 @@
         <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
@@ -8914,10 +8918,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8940,16 +8944,16 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8999,7 +9003,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9014,39 +9018,39 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS52" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9069,16 +9073,16 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9128,7 +9132,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9155,27 +9159,27 @@
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9198,19 +9202,19 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -9259,7 +9263,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9271,7 +9275,7 @@
         <v>85</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>85</v>
@@ -9289,10 +9293,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9303,10 +9307,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9430,10 +9434,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9559,14 +9563,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9588,10 +9592,10 @@
         <v>141</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>144</v>
@@ -9646,7 +9650,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9690,10 +9694,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9716,13 +9720,13 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9773,7 +9777,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9782,7 +9786,7 @@
         <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>107</v>
@@ -9803,10 +9807,10 @@
         <v>85</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9817,10 +9821,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9843,13 +9847,13 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9900,7 +9904,7 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9909,7 +9913,7 @@
         <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>107</v>
@@ -9930,10 +9934,10 @@
         <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -9944,10 +9948,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9973,16 +9977,16 @@
         <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
@@ -10010,10 +10014,10 @@
         <v>119</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>85</v>
@@ -10031,7 +10035,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10058,13 +10062,13 @@
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10075,10 +10079,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10104,16 +10108,16 @@
         <v>184</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
@@ -10138,13 +10142,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10162,7 +10166,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10189,13 +10193,13 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10206,10 +10210,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10232,17 +10236,17 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>85</v>
@@ -10291,7 +10295,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10324,7 +10328,7 @@
         <v>85</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10335,10 +10339,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10364,10 +10368,10 @@
         <v>162</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10418,7 +10422,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10448,10 +10452,10 @@
         <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10462,10 +10466,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10488,16 +10492,16 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10547,7 +10551,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10577,10 +10581,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10591,10 +10595,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10617,16 +10621,16 @@
         <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10676,7 +10680,7 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -10706,10 +10710,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10720,10 +10724,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10746,19 +10750,19 @@
         <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>85</v>
@@ -10807,7 +10811,7 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -10837,10 +10841,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -10851,10 +10855,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10978,10 +10982,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11107,14 +11111,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11136,10 +11140,10 @@
         <v>141</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>144</v>
@@ -11194,7 +11198,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11238,10 +11242,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11267,13 +11271,13 @@
         <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O70" t="s" s="2">
         <v>277</v>
@@ -11301,10 +11305,10 @@
         <v>85</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>279</v>
@@ -11325,7 +11329,7 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>95</v>
@@ -11352,7 +11356,7 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>282</v>
@@ -11369,10 +11373,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11395,19 +11399,19 @@
         <v>96</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11456,7 +11460,7 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11483,27 +11487,27 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11529,16 +11533,16 @@
         <v>184</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11566,10 +11570,10 @@
         <v>189</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>85</v>
@@ -11587,7 +11591,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -11596,7 +11600,7 @@
         <v>95</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>107</v>
@@ -11620,7 +11624,7 @@
         <v>138</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
@@ -11631,14 +11635,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11660,16 +11664,16 @@
         <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11697,10 +11701,10 @@
         <v>189</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>85</v>
@@ -11718,7 +11722,7 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
@@ -11745,27 +11749,27 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS73" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11791,16 +11795,16 @@
         <v>86</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
@@ -11849,7 +11853,7 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -11879,10 +11883,10 @@
         <v>85</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3096" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3096" uniqueCount="616">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -671,7 +671,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1476: source value from MICROBIOLOGY - IEN (63.05-.001)</t>
+    <t>1476: source value based on MICROBIOLOGY - IEN (63.05-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -937,7 +937,11 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1480: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case Not NULL</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+lomo-37-1480:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) {null}</t>
+  </si>
+  <si>
+    <t>1480: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) if Not NULL</t>
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
@@ -971,10 +975,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lomo-37-1480-1:undefined: if Not NULL then http://loinc.org {null}</t>
-  </si>
-  <si>
-    <t>1480-1: fixed value = http://loinc.org case Not NULL</t>
+lomo-37-1480-1:If (undefined) is Not NULL then fixed value http://loinc.org {null}</t>
+  </si>
+  <si>
+    <t>1480-1: fixed value = http://loinc.org if Not NULL</t>
   </si>
   <si>
     <t>C*E.3</t>
@@ -1019,7 +1023,11 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1480-2: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) case Not NULL</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+lomo-37-1480-2:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) {null}</t>
+  </si>
+  <si>
+    <t>1480-2: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) if Not NULL</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1043,7 +1051,11 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1480-3: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) case Not NULL</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+lomo-37-1480-3:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) {null}</t>
+  </si>
+  <si>
+    <t>1480-3: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) if Not NULL</t>
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
@@ -1123,7 +1135,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
+    <t>844: reference based on PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
@@ -1255,7 +1267,7 @@
 </t>
   </si>
   <si>
-    <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
+    <t>1450: source value based on MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime</t>
@@ -1277,7 +1289,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>1484: source value from MICROBIOLOGY - DATE REPORT COMPLETED (63.05-.03)</t>
+    <t>1484: source value based on MICROBIOLOGY - DATE REPORT COMPLETED (63.05-.03)</t>
   </si>
   <si>
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
@@ -1337,7 +1349,7 @@
 </t>
   </si>
   <si>
-    <t>1464: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
+    <t>1464: reference based on MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
   </si>
   <si>
     <t>Micro.Microbiology.AccessioningInstitutionIEN</t>
@@ -1356,7 +1368,7 @@
 </t>
   </si>
   <si>
-    <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
+    <t>1679: reference based on MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
   </si>
   <si>
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
@@ -1489,7 +1501,7 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
-    <t>1454: source value from MICROBIOLOGY - COMMENT ON SPECIMEN (63.05-.99)</t>
+    <t>1454: source value based on MICROBIOLOGY - COMMENT ON SPECIMEN (63.05-.99)</t>
   </si>
   <si>
     <t>Micro.Microbiology.SpecimenComment</t>
@@ -1578,7 +1590,7 @@
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
   </si>
   <si>
-    <t>1659: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (63.05-.06)</t>
+    <t>1659: reference based on MICROBIOLOGY - MICROBIOLOGY ACCESSION (63.05-.06)</t>
   </si>
   <si>
     <t>Micro.Microbiology.MicrobiologyAccession</t>
@@ -2288,7 +2300,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="250.93359375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="251.96875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="99.32421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
@@ -5897,10 +5909,10 @@
         <v>85</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>107</v>
+        <v>295</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>85</v>
@@ -5915,10 +5927,10 @@
         <v>85</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>85</v>
@@ -5929,10 +5941,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6056,10 +6068,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6185,10 +6197,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6214,16 +6226,16 @@
         <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>85</v>
@@ -6272,7 +6284,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6284,10 +6296,10 @@
         <v>85</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>85</v>
@@ -6302,10 +6314,10 @@
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>85</v>
@@ -6316,10 +6328,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6345,13 +6357,13 @@
         <v>162</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6401,7 +6413,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6431,10 +6443,10 @@
         <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>85</v>
@@ -6445,10 +6457,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6474,14 +6486,14 @@
         <v>115</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -6530,7 +6542,7 @@
         <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6542,10 +6554,10 @@
         <v>85</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>107</v>
+        <v>323</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>85</v>
@@ -6560,10 +6572,10 @@
         <v>85</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>85</v>
@@ -6574,10 +6586,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6603,14 +6615,14 @@
         <v>162</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -6659,7 +6671,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6671,10 +6683,10 @@
         <v>85</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>107</v>
+        <v>332</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>85</v>
@@ -6689,10 +6701,10 @@
         <v>85</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>85</v>
@@ -6703,10 +6715,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6729,19 +6741,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>85</v>
@@ -6790,7 +6802,7 @@
         <v>85</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6820,10 +6832,10 @@
         <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>85</v>
@@ -6834,10 +6846,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6863,16 +6875,16 @@
         <v>162</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>85</v>
@@ -6921,7 +6933,7 @@
         <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6951,10 +6963,10 @@
         <v>85</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>85</v>
@@ -6965,10 +6977,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6991,19 +7003,19 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -7052,7 +7064,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -7067,28 +7079,28 @@
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AS37" t="s" s="2">
         <v>85</v>
@@ -7096,10 +7108,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7122,16 +7134,16 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7181,7 +7193,7 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -7214,10 +7226,10 @@
         <v>282</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AS38" t="s" s="2">
         <v>85</v>
@@ -7225,14 +7237,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7251,19 +7263,19 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7312,7 +7324,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7336,19 +7348,19 @@
         <v>85</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>85</v>
@@ -7356,14 +7368,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7382,19 +7394,19 @@
         <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
@@ -7431,7 +7443,7 @@
         <v>85</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7441,7 +7453,7 @@
         <v>171</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7450,10 +7462,10 @@
         <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>85</v>
@@ -7465,19 +7477,19 @@
         <v>85</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>85</v>
@@ -7485,16 +7497,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7513,19 +7525,19 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>85</v>
@@ -7574,7 +7586,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7583,34 +7595,34 @@
         <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>85</v>
@@ -7618,10 +7630,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7644,16 +7656,16 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7703,7 +7715,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7718,13 +7730,13 @@
         <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>85</v>
@@ -7733,13 +7745,13 @@
         <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>85</v>
@@ -7747,10 +7759,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7773,17 +7785,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -7820,7 +7832,7 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7830,7 +7842,7 @@
         <v>171</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7854,19 +7866,19 @@
         <v>85</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -7874,13 +7886,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
@@ -7902,17 +7914,17 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -7961,7 +7973,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7976,28 +7988,28 @@
         <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>85</v>
@@ -8005,13 +8017,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8033,17 +8045,17 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8092,7 +8104,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8107,28 +8119,28 @@
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>85</v>
@@ -8136,10 +8148,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8162,19 +8174,19 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8223,7 +8235,7 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8232,10 +8244,10 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8250,27 +8262,27 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8296,16 +8308,16 @@
         <v>184</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8334,7 +8346,7 @@
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>85</v>
@@ -8352,7 +8364,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8361,13 +8373,13 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>85</v>
@@ -8385,7 +8397,7 @@
         <v>138</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
@@ -8396,14 +8408,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8425,16 +8437,16 @@
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8462,10 +8474,10 @@
         <v>189</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8483,7 +8495,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8510,27 +8522,27 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8553,19 +8565,19 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8614,7 +8626,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8629,10 +8641,10 @@
         <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>85</v>
@@ -8644,10 +8656,10 @@
         <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -8658,10 +8670,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8687,13 +8699,13 @@
         <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8719,13 +8731,13 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8743,7 +8755,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8770,27 +8782,27 @@
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS50" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8816,16 +8828,16 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -8850,13 +8862,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8874,7 +8886,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8904,10 +8916,10 @@
         <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
@@ -8918,10 +8930,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8944,16 +8956,16 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9003,7 +9015,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9018,39 +9030,39 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS52" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9073,16 +9085,16 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9132,7 +9144,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9159,27 +9171,27 @@
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9202,19 +9214,19 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -9263,7 +9275,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9275,7 +9287,7 @@
         <v>85</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>85</v>
@@ -9293,10 +9305,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9307,10 +9319,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9434,10 +9446,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9563,14 +9575,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9592,10 +9604,10 @@
         <v>141</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>144</v>
@@ -9650,7 +9662,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9694,10 +9706,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9720,13 +9732,13 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9777,7 +9789,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9786,7 +9798,7 @@
         <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>107</v>
@@ -9807,10 +9819,10 @@
         <v>85</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9821,10 +9833,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9847,13 +9859,13 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9904,7 +9916,7 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9913,7 +9925,7 @@
         <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>107</v>
@@ -9934,10 +9946,10 @@
         <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -9948,10 +9960,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9977,16 +9989,16 @@
         <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
@@ -10014,10 +10026,10 @@
         <v>119</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>85</v>
@@ -10035,7 +10047,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10062,13 +10074,13 @@
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10079,10 +10091,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10108,16 +10120,16 @@
         <v>184</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
@@ -10142,13 +10154,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10166,7 +10178,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10193,13 +10205,13 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10210,10 +10222,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10236,17 +10248,17 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>85</v>
@@ -10295,7 +10307,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10328,7 +10340,7 @@
         <v>85</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10339,10 +10351,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10368,10 +10380,10 @@
         <v>162</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10422,7 +10434,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10452,10 +10464,10 @@
         <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10466,10 +10478,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10492,16 +10504,16 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10551,7 +10563,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10581,10 +10593,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10595,10 +10607,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10621,16 +10633,16 @@
         <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10680,7 +10692,7 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -10710,10 +10722,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10724,10 +10736,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10750,19 +10762,19 @@
         <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>85</v>
@@ -10811,7 +10823,7 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -10841,10 +10853,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -10855,10 +10867,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10982,10 +10994,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11111,14 +11123,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11140,10 +11152,10 @@
         <v>141</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>144</v>
@@ -11198,7 +11210,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11242,10 +11254,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11271,13 +11283,13 @@
         <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="O70" t="s" s="2">
         <v>277</v>
@@ -11305,10 +11317,10 @@
         <v>85</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>279</v>
@@ -11329,7 +11341,7 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>95</v>
@@ -11356,7 +11368,7 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>282</v>
@@ -11373,10 +11385,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11399,19 +11411,19 @@
         <v>96</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11460,7 +11472,7 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11487,27 +11499,27 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11533,16 +11545,16 @@
         <v>184</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11570,10 +11582,10 @@
         <v>189</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>85</v>
@@ -11591,7 +11603,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -11600,7 +11612,7 @@
         <v>95</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>107</v>
@@ -11624,7 +11636,7 @@
         <v>138</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
@@ -11635,14 +11647,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11664,16 +11676,16 @@
         <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11701,10 +11713,10 @@
         <v>189</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>85</v>
@@ -11722,7 +11734,7 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
@@ -11749,27 +11761,27 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS73" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11795,16 +11807,16 @@
         <v>86</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
@@ -11853,7 +11865,7 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -11883,10 +11895,10 @@
         <v>85</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -938,7 +938,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lomo-37-1480:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) {null}</t>
+lomo-37-1480:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) {true}</t>
   </si>
   <si>
     <t>1480: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) if Not NULL</t>
@@ -975,7 +975,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lomo-37-1480-1:If (undefined) is Not NULL then fixed value http://loinc.org {null}</t>
+lomo-37-1480-1:If Not NULL then fixed value http://loinc.org {true}</t>
   </si>
   <si>
     <t>1480-1: fixed value = http://loinc.org if Not NULL</t>
@@ -1024,7 +1024,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lomo-37-1480-2:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) {null}</t>
+lomo-37-1480-2:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) {true}</t>
   </si>
   <si>
     <t>1480-2: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) if Not NULL</t>
@@ -1052,7 +1052,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lomo-37-1480-3:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) {null}</t>
+lomo-37-1480-3:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) {true}</t>
   </si>
   <si>
     <t>1480-3: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) if Not NULL</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -831,6 +831,28 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:Laboratory</t>
+  </si>
+  <si>
+    <t>Laboratory</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -841,29 +863,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
     <t>843: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#laboratory</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:Laboratory</t>
-  </si>
-  <si>
-    <t>Laboratory</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -5209,7 +5209,7 @@
         <v>85</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>263</v>
+        <v>85</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>85</v>
@@ -5227,16 +5227,16 @@
         <v>119</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Z23" t="s" s="2">
+      <c r="AA23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB23" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5261,28 +5261,28 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AR23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AR23" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>85</v>
@@ -5290,13 +5290,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>258</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>85</v>
@@ -5340,7 +5340,7 @@
         <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>85</v>
@@ -5358,10 +5358,10 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -5394,7 +5394,7 @@
         <v>107</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>85</v>
+        <v>271</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>85</v>
@@ -5412,10 +5412,10 @@
         <v>85</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
